--- a/dataset/lecture_3_output/EFCP6_output.xlsx
+++ b/dataset/lecture_3_output/EFCP6_output.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,5132 +429,5132 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>CAS</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>PubChem_CID</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_2</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_3</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_4</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_5</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_6</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_7</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_8</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_9</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_10</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_11</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_12</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_13</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_14</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_15</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_16</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_17</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_18</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_19</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_20</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_21</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_22</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_23</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_24</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_25</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_26</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_27</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_28</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_29</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_30</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_31</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_32</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_33</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_34</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_35</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_36</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_37</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_38</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_39</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_40</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_41</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_42</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_43</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_44</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_45</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_46</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_47</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_48</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_49</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_50</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_51</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_52</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_53</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_54</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_55</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_56</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_57</t>
         </is>
       </c>
-      <c r="BH1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_58</t>
         </is>
       </c>
-      <c r="BI1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_59</t>
         </is>
       </c>
-      <c r="BJ1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_60</t>
         </is>
       </c>
-      <c r="BK1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_61</t>
         </is>
       </c>
-      <c r="BL1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_62</t>
         </is>
       </c>
-      <c r="BM1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_63</t>
         </is>
       </c>
-      <c r="BN1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_64</t>
         </is>
       </c>
-      <c r="BO1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_65</t>
         </is>
       </c>
-      <c r="BP1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_66</t>
         </is>
       </c>
-      <c r="BQ1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_67</t>
         </is>
       </c>
-      <c r="BR1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_68</t>
         </is>
       </c>
-      <c r="BS1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_69</t>
         </is>
       </c>
-      <c r="BT1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_70</t>
         </is>
       </c>
-      <c r="BU1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_71</t>
         </is>
       </c>
-      <c r="BV1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_72</t>
         </is>
       </c>
-      <c r="BW1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_73</t>
         </is>
       </c>
-      <c r="BX1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_74</t>
         </is>
       </c>
-      <c r="BY1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_75</t>
         </is>
       </c>
-      <c r="BZ1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_76</t>
         </is>
       </c>
-      <c r="CA1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_77</t>
         </is>
       </c>
-      <c r="CB1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_78</t>
         </is>
       </c>
-      <c r="CC1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_79</t>
         </is>
       </c>
-      <c r="CD1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_80</t>
         </is>
       </c>
-      <c r="CE1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_81</t>
         </is>
       </c>
-      <c r="CF1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_82</t>
         </is>
       </c>
-      <c r="CG1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_83</t>
         </is>
       </c>
-      <c r="CH1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_84</t>
         </is>
       </c>
-      <c r="CI1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_85</t>
         </is>
       </c>
-      <c r="CJ1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_86</t>
         </is>
       </c>
-      <c r="CK1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_87</t>
         </is>
       </c>
-      <c r="CL1" t="inlineStr">
+      <c r="CL1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_88</t>
         </is>
       </c>
-      <c r="CM1" t="inlineStr">
+      <c r="CM1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_89</t>
         </is>
       </c>
-      <c r="CN1" t="inlineStr">
+      <c r="CN1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_90</t>
         </is>
       </c>
-      <c r="CO1" t="inlineStr">
+      <c r="CO1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_91</t>
         </is>
       </c>
-      <c r="CP1" t="inlineStr">
+      <c r="CP1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_92</t>
         </is>
       </c>
-      <c r="CQ1" t="inlineStr">
+      <c r="CQ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_93</t>
         </is>
       </c>
-      <c r="CR1" t="inlineStr">
+      <c r="CR1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_94</t>
         </is>
       </c>
-      <c r="CS1" t="inlineStr">
+      <c r="CS1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_95</t>
         </is>
       </c>
-      <c r="CT1" t="inlineStr">
+      <c r="CT1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_96</t>
         </is>
       </c>
-      <c r="CU1" t="inlineStr">
+      <c r="CU1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_97</t>
         </is>
       </c>
-      <c r="CV1" t="inlineStr">
+      <c r="CV1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_98</t>
         </is>
       </c>
-      <c r="CW1" t="inlineStr">
+      <c r="CW1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_99</t>
         </is>
       </c>
-      <c r="CX1" t="inlineStr">
+      <c r="CX1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_100</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
+      <c r="CY1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_101</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="CZ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_102</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
+      <c r="DA1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_103</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DB1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_104</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DC1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_105</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DD1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_106</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DE1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_107</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DF1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_108</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DG1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_109</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="DH1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_110</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="DI1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_111</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="DJ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_112</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="DK1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_113</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="DL1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_114</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="DM1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_115</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="DN1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_116</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="DO1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_117</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="DP1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_118</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="DQ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_119</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="DR1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_120</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="DS1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_121</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="DT1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_122</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="DU1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_123</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
+      <c r="DV1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_124</t>
         </is>
       </c>
-      <c r="DW1" t="inlineStr">
+      <c r="DW1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_125</t>
         </is>
       </c>
-      <c r="DX1" t="inlineStr">
+      <c r="DX1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_126</t>
         </is>
       </c>
-      <c r="DY1" t="inlineStr">
+      <c r="DY1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_127</t>
         </is>
       </c>
-      <c r="DZ1" t="inlineStr">
+      <c r="DZ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_128</t>
         </is>
       </c>
-      <c r="EA1" t="inlineStr">
+      <c r="EA1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_129</t>
         </is>
       </c>
-      <c r="EB1" t="inlineStr">
+      <c r="EB1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_130</t>
         </is>
       </c>
-      <c r="EC1" t="inlineStr">
+      <c r="EC1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_131</t>
         </is>
       </c>
-      <c r="ED1" t="inlineStr">
+      <c r="ED1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_132</t>
         </is>
       </c>
-      <c r="EE1" t="inlineStr">
+      <c r="EE1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_133</t>
         </is>
       </c>
-      <c r="EF1" t="inlineStr">
+      <c r="EF1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_134</t>
         </is>
       </c>
-      <c r="EG1" t="inlineStr">
+      <c r="EG1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_135</t>
         </is>
       </c>
-      <c r="EH1" t="inlineStr">
+      <c r="EH1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_136</t>
         </is>
       </c>
-      <c r="EI1" t="inlineStr">
+      <c r="EI1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_137</t>
         </is>
       </c>
-      <c r="EJ1" t="inlineStr">
+      <c r="EJ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_138</t>
         </is>
       </c>
-      <c r="EK1" t="inlineStr">
+      <c r="EK1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_139</t>
         </is>
       </c>
-      <c r="EL1" t="inlineStr">
+      <c r="EL1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_140</t>
         </is>
       </c>
-      <c r="EM1" t="inlineStr">
+      <c r="EM1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_141</t>
         </is>
       </c>
-      <c r="EN1" t="inlineStr">
+      <c r="EN1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_142</t>
         </is>
       </c>
-      <c r="EO1" t="inlineStr">
+      <c r="EO1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_143</t>
         </is>
       </c>
-      <c r="EP1" t="inlineStr">
+      <c r="EP1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_144</t>
         </is>
       </c>
-      <c r="EQ1" t="inlineStr">
+      <c r="EQ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_145</t>
         </is>
       </c>
-      <c r="ER1" t="inlineStr">
+      <c r="ER1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_146</t>
         </is>
       </c>
-      <c r="ES1" t="inlineStr">
+      <c r="ES1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_147</t>
         </is>
       </c>
-      <c r="ET1" t="inlineStr">
+      <c r="ET1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_148</t>
         </is>
       </c>
-      <c r="EU1" t="inlineStr">
+      <c r="EU1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_149</t>
         </is>
       </c>
-      <c r="EV1" t="inlineStr">
+      <c r="EV1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_150</t>
         </is>
       </c>
-      <c r="EW1" t="inlineStr">
+      <c r="EW1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_151</t>
         </is>
       </c>
-      <c r="EX1" t="inlineStr">
+      <c r="EX1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_152</t>
         </is>
       </c>
-      <c r="EY1" t="inlineStr">
+      <c r="EY1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_153</t>
         </is>
       </c>
-      <c r="EZ1" t="inlineStr">
+      <c r="EZ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_154</t>
         </is>
       </c>
-      <c r="FA1" t="inlineStr">
+      <c r="FA1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_155</t>
         </is>
       </c>
-      <c r="FB1" t="inlineStr">
+      <c r="FB1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_156</t>
         </is>
       </c>
-      <c r="FC1" t="inlineStr">
+      <c r="FC1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_157</t>
         </is>
       </c>
-      <c r="FD1" t="inlineStr">
+      <c r="FD1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_158</t>
         </is>
       </c>
-      <c r="FE1" t="inlineStr">
+      <c r="FE1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_159</t>
         </is>
       </c>
-      <c r="FF1" t="inlineStr">
+      <c r="FF1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_160</t>
         </is>
       </c>
-      <c r="FG1" t="inlineStr">
+      <c r="FG1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_161</t>
         </is>
       </c>
-      <c r="FH1" t="inlineStr">
+      <c r="FH1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_162</t>
         </is>
       </c>
-      <c r="FI1" t="inlineStr">
+      <c r="FI1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_163</t>
         </is>
       </c>
-      <c r="FJ1" t="inlineStr">
+      <c r="FJ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_164</t>
         </is>
       </c>
-      <c r="FK1" t="inlineStr">
+      <c r="FK1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_165</t>
         </is>
       </c>
-      <c r="FL1" t="inlineStr">
+      <c r="FL1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_166</t>
         </is>
       </c>
-      <c r="FM1" t="inlineStr">
+      <c r="FM1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_167</t>
         </is>
       </c>
-      <c r="FN1" t="inlineStr">
+      <c r="FN1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_168</t>
         </is>
       </c>
-      <c r="FO1" t="inlineStr">
+      <c r="FO1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_169</t>
         </is>
       </c>
-      <c r="FP1" t="inlineStr">
+      <c r="FP1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_170</t>
         </is>
       </c>
-      <c r="FQ1" t="inlineStr">
+      <c r="FQ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_171</t>
         </is>
       </c>
-      <c r="FR1" t="inlineStr">
+      <c r="FR1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_172</t>
         </is>
       </c>
-      <c r="FS1" t="inlineStr">
+      <c r="FS1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_173</t>
         </is>
       </c>
-      <c r="FT1" t="inlineStr">
+      <c r="FT1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_174</t>
         </is>
       </c>
-      <c r="FU1" t="inlineStr">
+      <c r="FU1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_175</t>
         </is>
       </c>
-      <c r="FV1" t="inlineStr">
+      <c r="FV1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_176</t>
         </is>
       </c>
-      <c r="FW1" t="inlineStr">
+      <c r="FW1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_177</t>
         </is>
       </c>
-      <c r="FX1" t="inlineStr">
+      <c r="FX1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_178</t>
         </is>
       </c>
-      <c r="FY1" t="inlineStr">
+      <c r="FY1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_179</t>
         </is>
       </c>
-      <c r="FZ1" t="inlineStr">
+      <c r="FZ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_180</t>
         </is>
       </c>
-      <c r="GA1" t="inlineStr">
+      <c r="GA1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_181</t>
         </is>
       </c>
-      <c r="GB1" t="inlineStr">
+      <c r="GB1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_182</t>
         </is>
       </c>
-      <c r="GC1" t="inlineStr">
+      <c r="GC1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_183</t>
         </is>
       </c>
-      <c r="GD1" t="inlineStr">
+      <c r="GD1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_184</t>
         </is>
       </c>
-      <c r="GE1" t="inlineStr">
+      <c r="GE1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_185</t>
         </is>
       </c>
-      <c r="GF1" t="inlineStr">
+      <c r="GF1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_186</t>
         </is>
       </c>
-      <c r="GG1" t="inlineStr">
+      <c r="GG1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_187</t>
         </is>
       </c>
-      <c r="GH1" t="inlineStr">
+      <c r="GH1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_188</t>
         </is>
       </c>
-      <c r="GI1" t="inlineStr">
+      <c r="GI1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_189</t>
         </is>
       </c>
-      <c r="GJ1" t="inlineStr">
+      <c r="GJ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_190</t>
         </is>
       </c>
-      <c r="GK1" t="inlineStr">
+      <c r="GK1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_191</t>
         </is>
       </c>
-      <c r="GL1" t="inlineStr">
+      <c r="GL1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_192</t>
         </is>
       </c>
-      <c r="GM1" t="inlineStr">
+      <c r="GM1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_193</t>
         </is>
       </c>
-      <c r="GN1" t="inlineStr">
+      <c r="GN1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_194</t>
         </is>
       </c>
-      <c r="GO1" t="inlineStr">
+      <c r="GO1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_195</t>
         </is>
       </c>
-      <c r="GP1" t="inlineStr">
+      <c r="GP1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_196</t>
         </is>
       </c>
-      <c r="GQ1" t="inlineStr">
+      <c r="GQ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_197</t>
         </is>
       </c>
-      <c r="GR1" t="inlineStr">
+      <c r="GR1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_198</t>
         </is>
       </c>
-      <c r="GS1" t="inlineStr">
+      <c r="GS1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_199</t>
         </is>
       </c>
-      <c r="GT1" t="inlineStr">
+      <c r="GT1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_200</t>
         </is>
       </c>
-      <c r="GU1" t="inlineStr">
+      <c r="GU1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_201</t>
         </is>
       </c>
-      <c r="GV1" t="inlineStr">
+      <c r="GV1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_202</t>
         </is>
       </c>
-      <c r="GW1" t="inlineStr">
+      <c r="GW1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_203</t>
         </is>
       </c>
-      <c r="GX1" t="inlineStr">
+      <c r="GX1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_204</t>
         </is>
       </c>
-      <c r="GY1" t="inlineStr">
+      <c r="GY1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_205</t>
         </is>
       </c>
-      <c r="GZ1" t="inlineStr">
+      <c r="GZ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_206</t>
         </is>
       </c>
-      <c r="HA1" t="inlineStr">
+      <c r="HA1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_207</t>
         </is>
       </c>
-      <c r="HB1" t="inlineStr">
+      <c r="HB1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_208</t>
         </is>
       </c>
-      <c r="HC1" t="inlineStr">
+      <c r="HC1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_209</t>
         </is>
       </c>
-      <c r="HD1" t="inlineStr">
+      <c r="HD1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_210</t>
         </is>
       </c>
-      <c r="HE1" t="inlineStr">
+      <c r="HE1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_211</t>
         </is>
       </c>
-      <c r="HF1" t="inlineStr">
+      <c r="HF1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_212</t>
         </is>
       </c>
-      <c r="HG1" t="inlineStr">
+      <c r="HG1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_213</t>
         </is>
       </c>
-      <c r="HH1" t="inlineStr">
+      <c r="HH1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_214</t>
         </is>
       </c>
-      <c r="HI1" t="inlineStr">
+      <c r="HI1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_215</t>
         </is>
       </c>
-      <c r="HJ1" t="inlineStr">
+      <c r="HJ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_216</t>
         </is>
       </c>
-      <c r="HK1" t="inlineStr">
+      <c r="HK1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_217</t>
         </is>
       </c>
-      <c r="HL1" t="inlineStr">
+      <c r="HL1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_218</t>
         </is>
       </c>
-      <c r="HM1" t="inlineStr">
+      <c r="HM1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_219</t>
         </is>
       </c>
-      <c r="HN1" t="inlineStr">
+      <c r="HN1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_220</t>
         </is>
       </c>
-      <c r="HO1" t="inlineStr">
+      <c r="HO1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_221</t>
         </is>
       </c>
-      <c r="HP1" t="inlineStr">
+      <c r="HP1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_222</t>
         </is>
       </c>
-      <c r="HQ1" t="inlineStr">
+      <c r="HQ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_223</t>
         </is>
       </c>
-      <c r="HR1" t="inlineStr">
+      <c r="HR1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_224</t>
         </is>
       </c>
-      <c r="HS1" t="inlineStr">
+      <c r="HS1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_225</t>
         </is>
       </c>
-      <c r="HT1" t="inlineStr">
+      <c r="HT1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_226</t>
         </is>
       </c>
-      <c r="HU1" t="inlineStr">
+      <c r="HU1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_227</t>
         </is>
       </c>
-      <c r="HV1" t="inlineStr">
+      <c r="HV1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_228</t>
         </is>
       </c>
-      <c r="HW1" t="inlineStr">
+      <c r="HW1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_229</t>
         </is>
       </c>
-      <c r="HX1" t="inlineStr">
+      <c r="HX1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_230</t>
         </is>
       </c>
-      <c r="HY1" t="inlineStr">
+      <c r="HY1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_231</t>
         </is>
       </c>
-      <c r="HZ1" t="inlineStr">
+      <c r="HZ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_232</t>
         </is>
       </c>
-      <c r="IA1" t="inlineStr">
+      <c r="IA1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_233</t>
         </is>
       </c>
-      <c r="IB1" t="inlineStr">
+      <c r="IB1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_234</t>
         </is>
       </c>
-      <c r="IC1" t="inlineStr">
+      <c r="IC1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_235</t>
         </is>
       </c>
-      <c r="ID1" t="inlineStr">
+      <c r="ID1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_236</t>
         </is>
       </c>
-      <c r="IE1" t="inlineStr">
+      <c r="IE1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_237</t>
         </is>
       </c>
-      <c r="IF1" t="inlineStr">
+      <c r="IF1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_238</t>
         </is>
       </c>
-      <c r="IG1" t="inlineStr">
+      <c r="IG1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_239</t>
         </is>
       </c>
-      <c r="IH1" t="inlineStr">
+      <c r="IH1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_240</t>
         </is>
       </c>
-      <c r="II1" t="inlineStr">
+      <c r="II1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_241</t>
         </is>
       </c>
-      <c r="IJ1" t="inlineStr">
+      <c r="IJ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_242</t>
         </is>
       </c>
-      <c r="IK1" t="inlineStr">
+      <c r="IK1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_243</t>
         </is>
       </c>
-      <c r="IL1" t="inlineStr">
+      <c r="IL1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_244</t>
         </is>
       </c>
-      <c r="IM1" t="inlineStr">
+      <c r="IM1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_245</t>
         </is>
       </c>
-      <c r="IN1" t="inlineStr">
+      <c r="IN1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_246</t>
         </is>
       </c>
-      <c r="IO1" t="inlineStr">
+      <c r="IO1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_247</t>
         </is>
       </c>
-      <c r="IP1" t="inlineStr">
+      <c r="IP1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_248</t>
         </is>
       </c>
-      <c r="IQ1" t="inlineStr">
+      <c r="IQ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_249</t>
         </is>
       </c>
-      <c r="IR1" t="inlineStr">
+      <c r="IR1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_250</t>
         </is>
       </c>
-      <c r="IS1" t="inlineStr">
+      <c r="IS1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_251</t>
         </is>
       </c>
-      <c r="IT1" t="inlineStr">
+      <c r="IT1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_252</t>
         </is>
       </c>
-      <c r="IU1" t="inlineStr">
+      <c r="IU1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_253</t>
         </is>
       </c>
-      <c r="IV1" t="inlineStr">
+      <c r="IV1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_254</t>
         </is>
       </c>
-      <c r="IW1" t="inlineStr">
+      <c r="IW1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_255</t>
         </is>
       </c>
-      <c r="IX1" t="inlineStr">
+      <c r="IX1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_256</t>
         </is>
       </c>
-      <c r="IY1" t="inlineStr">
+      <c r="IY1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_257</t>
         </is>
       </c>
-      <c r="IZ1" t="inlineStr">
+      <c r="IZ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_258</t>
         </is>
       </c>
-      <c r="JA1" t="inlineStr">
+      <c r="JA1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_259</t>
         </is>
       </c>
-      <c r="JB1" t="inlineStr">
+      <c r="JB1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_260</t>
         </is>
       </c>
-      <c r="JC1" t="inlineStr">
+      <c r="JC1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_261</t>
         </is>
       </c>
-      <c r="JD1" t="inlineStr">
+      <c r="JD1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_262</t>
         </is>
       </c>
-      <c r="JE1" t="inlineStr">
+      <c r="JE1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_263</t>
         </is>
       </c>
-      <c r="JF1" t="inlineStr">
+      <c r="JF1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_264</t>
         </is>
       </c>
-      <c r="JG1" t="inlineStr">
+      <c r="JG1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_265</t>
         </is>
       </c>
-      <c r="JH1" t="inlineStr">
+      <c r="JH1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_266</t>
         </is>
       </c>
-      <c r="JI1" t="inlineStr">
+      <c r="JI1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_267</t>
         </is>
       </c>
-      <c r="JJ1" t="inlineStr">
+      <c r="JJ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_268</t>
         </is>
       </c>
-      <c r="JK1" t="inlineStr">
+      <c r="JK1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_269</t>
         </is>
       </c>
-      <c r="JL1" t="inlineStr">
+      <c r="JL1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_270</t>
         </is>
       </c>
-      <c r="JM1" t="inlineStr">
+      <c r="JM1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_271</t>
         </is>
       </c>
-      <c r="JN1" t="inlineStr">
+      <c r="JN1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_272</t>
         </is>
       </c>
-      <c r="JO1" t="inlineStr">
+      <c r="JO1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_273</t>
         </is>
       </c>
-      <c r="JP1" t="inlineStr">
+      <c r="JP1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_274</t>
         </is>
       </c>
-      <c r="JQ1" t="inlineStr">
+      <c r="JQ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_275</t>
         </is>
       </c>
-      <c r="JR1" t="inlineStr">
+      <c r="JR1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_276</t>
         </is>
       </c>
-      <c r="JS1" t="inlineStr">
+      <c r="JS1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_277</t>
         </is>
       </c>
-      <c r="JT1" t="inlineStr">
+      <c r="JT1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_278</t>
         </is>
       </c>
-      <c r="JU1" t="inlineStr">
+      <c r="JU1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_279</t>
         </is>
       </c>
-      <c r="JV1" t="inlineStr">
+      <c r="JV1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_280</t>
         </is>
       </c>
-      <c r="JW1" t="inlineStr">
+      <c r="JW1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_281</t>
         </is>
       </c>
-      <c r="JX1" t="inlineStr">
+      <c r="JX1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_282</t>
         </is>
       </c>
-      <c r="JY1" t="inlineStr">
+      <c r="JY1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_283</t>
         </is>
       </c>
-      <c r="JZ1" t="inlineStr">
+      <c r="JZ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_284</t>
         </is>
       </c>
-      <c r="KA1" t="inlineStr">
+      <c r="KA1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_285</t>
         </is>
       </c>
-      <c r="KB1" t="inlineStr">
+      <c r="KB1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_286</t>
         </is>
       </c>
-      <c r="KC1" t="inlineStr">
+      <c r="KC1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_287</t>
         </is>
       </c>
-      <c r="KD1" t="inlineStr">
+      <c r="KD1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_288</t>
         </is>
       </c>
-      <c r="KE1" t="inlineStr">
+      <c r="KE1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_289</t>
         </is>
       </c>
-      <c r="KF1" t="inlineStr">
+      <c r="KF1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_290</t>
         </is>
       </c>
-      <c r="KG1" t="inlineStr">
+      <c r="KG1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_291</t>
         </is>
       </c>
-      <c r="KH1" t="inlineStr">
+      <c r="KH1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_292</t>
         </is>
       </c>
-      <c r="KI1" t="inlineStr">
+      <c r="KI1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_293</t>
         </is>
       </c>
-      <c r="KJ1" t="inlineStr">
+      <c r="KJ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_294</t>
         </is>
       </c>
-      <c r="KK1" t="inlineStr">
+      <c r="KK1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_295</t>
         </is>
       </c>
-      <c r="KL1" t="inlineStr">
+      <c r="KL1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_296</t>
         </is>
       </c>
-      <c r="KM1" t="inlineStr">
+      <c r="KM1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_297</t>
         </is>
       </c>
-      <c r="KN1" t="inlineStr">
+      <c r="KN1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_298</t>
         </is>
       </c>
-      <c r="KO1" t="inlineStr">
+      <c r="KO1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_299</t>
         </is>
       </c>
-      <c r="KP1" t="inlineStr">
+      <c r="KP1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_300</t>
         </is>
       </c>
-      <c r="KQ1" t="inlineStr">
+      <c r="KQ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_301</t>
         </is>
       </c>
-      <c r="KR1" t="inlineStr">
+      <c r="KR1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_302</t>
         </is>
       </c>
-      <c r="KS1" t="inlineStr">
+      <c r="KS1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_303</t>
         </is>
       </c>
-      <c r="KT1" t="inlineStr">
+      <c r="KT1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_304</t>
         </is>
       </c>
-      <c r="KU1" t="inlineStr">
+      <c r="KU1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_305</t>
         </is>
       </c>
-      <c r="KV1" t="inlineStr">
+      <c r="KV1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_306</t>
         </is>
       </c>
-      <c r="KW1" t="inlineStr">
+      <c r="KW1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_307</t>
         </is>
       </c>
-      <c r="KX1" t="inlineStr">
+      <c r="KX1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_308</t>
         </is>
       </c>
-      <c r="KY1" t="inlineStr">
+      <c r="KY1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_309</t>
         </is>
       </c>
-      <c r="KZ1" t="inlineStr">
+      <c r="KZ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_310</t>
         </is>
       </c>
-      <c r="LA1" t="inlineStr">
+      <c r="LA1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_311</t>
         </is>
       </c>
-      <c r="LB1" t="inlineStr">
+      <c r="LB1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_312</t>
         </is>
       </c>
-      <c r="LC1" t="inlineStr">
+      <c r="LC1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_313</t>
         </is>
       </c>
-      <c r="LD1" t="inlineStr">
+      <c r="LD1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_314</t>
         </is>
       </c>
-      <c r="LE1" t="inlineStr">
+      <c r="LE1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_315</t>
         </is>
       </c>
-      <c r="LF1" t="inlineStr">
+      <c r="LF1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_316</t>
         </is>
       </c>
-      <c r="LG1" t="inlineStr">
+      <c r="LG1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_317</t>
         </is>
       </c>
-      <c r="LH1" t="inlineStr">
+      <c r="LH1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_318</t>
         </is>
       </c>
-      <c r="LI1" t="inlineStr">
+      <c r="LI1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_319</t>
         </is>
       </c>
-      <c r="LJ1" t="inlineStr">
+      <c r="LJ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_320</t>
         </is>
       </c>
-      <c r="LK1" t="inlineStr">
+      <c r="LK1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_321</t>
         </is>
       </c>
-      <c r="LL1" t="inlineStr">
+      <c r="LL1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_322</t>
         </is>
       </c>
-      <c r="LM1" t="inlineStr">
+      <c r="LM1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_323</t>
         </is>
       </c>
-      <c r="LN1" t="inlineStr">
+      <c r="LN1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_324</t>
         </is>
       </c>
-      <c r="LO1" t="inlineStr">
+      <c r="LO1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_325</t>
         </is>
       </c>
-      <c r="LP1" t="inlineStr">
+      <c r="LP1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_326</t>
         </is>
       </c>
-      <c r="LQ1" t="inlineStr">
+      <c r="LQ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_327</t>
         </is>
       </c>
-      <c r="LR1" t="inlineStr">
+      <c r="LR1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_328</t>
         </is>
       </c>
-      <c r="LS1" t="inlineStr">
+      <c r="LS1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_329</t>
         </is>
       </c>
-      <c r="LT1" t="inlineStr">
+      <c r="LT1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_330</t>
         </is>
       </c>
-      <c r="LU1" t="inlineStr">
+      <c r="LU1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_331</t>
         </is>
       </c>
-      <c r="LV1" t="inlineStr">
+      <c r="LV1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_332</t>
         </is>
       </c>
-      <c r="LW1" t="inlineStr">
+      <c r="LW1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_333</t>
         </is>
       </c>
-      <c r="LX1" t="inlineStr">
+      <c r="LX1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_334</t>
         </is>
       </c>
-      <c r="LY1" t="inlineStr">
+      <c r="LY1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_335</t>
         </is>
       </c>
-      <c r="LZ1" t="inlineStr">
+      <c r="LZ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_336</t>
         </is>
       </c>
-      <c r="MA1" t="inlineStr">
+      <c r="MA1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_337</t>
         </is>
       </c>
-      <c r="MB1" t="inlineStr">
+      <c r="MB1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_338</t>
         </is>
       </c>
-      <c r="MC1" t="inlineStr">
+      <c r="MC1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_339</t>
         </is>
       </c>
-      <c r="MD1" t="inlineStr">
+      <c r="MD1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_340</t>
         </is>
       </c>
-      <c r="ME1" t="inlineStr">
+      <c r="ME1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_341</t>
         </is>
       </c>
-      <c r="MF1" t="inlineStr">
+      <c r="MF1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_342</t>
         </is>
       </c>
-      <c r="MG1" t="inlineStr">
+      <c r="MG1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_343</t>
         </is>
       </c>
-      <c r="MH1" t="inlineStr">
+      <c r="MH1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_344</t>
         </is>
       </c>
-      <c r="MI1" t="inlineStr">
+      <c r="MI1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_345</t>
         </is>
       </c>
-      <c r="MJ1" t="inlineStr">
+      <c r="MJ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_346</t>
         </is>
       </c>
-      <c r="MK1" t="inlineStr">
+      <c r="MK1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_347</t>
         </is>
       </c>
-      <c r="ML1" t="inlineStr">
+      <c r="ML1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_348</t>
         </is>
       </c>
-      <c r="MM1" t="inlineStr">
+      <c r="MM1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_349</t>
         </is>
       </c>
-      <c r="MN1" t="inlineStr">
+      <c r="MN1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_350</t>
         </is>
       </c>
-      <c r="MO1" t="inlineStr">
+      <c r="MO1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_351</t>
         </is>
       </c>
-      <c r="MP1" t="inlineStr">
+      <c r="MP1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_352</t>
         </is>
       </c>
-      <c r="MQ1" t="inlineStr">
+      <c r="MQ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_353</t>
         </is>
       </c>
-      <c r="MR1" t="inlineStr">
+      <c r="MR1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_354</t>
         </is>
       </c>
-      <c r="MS1" t="inlineStr">
+      <c r="MS1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_355</t>
         </is>
       </c>
-      <c r="MT1" t="inlineStr">
+      <c r="MT1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_356</t>
         </is>
       </c>
-      <c r="MU1" t="inlineStr">
+      <c r="MU1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_357</t>
         </is>
       </c>
-      <c r="MV1" t="inlineStr">
+      <c r="MV1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_358</t>
         </is>
       </c>
-      <c r="MW1" t="inlineStr">
+      <c r="MW1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_359</t>
         </is>
       </c>
-      <c r="MX1" t="inlineStr">
+      <c r="MX1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_360</t>
         </is>
       </c>
-      <c r="MY1" t="inlineStr">
+      <c r="MY1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_361</t>
         </is>
       </c>
-      <c r="MZ1" t="inlineStr">
+      <c r="MZ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_362</t>
         </is>
       </c>
-      <c r="NA1" t="inlineStr">
+      <c r="NA1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_363</t>
         </is>
       </c>
-      <c r="NB1" t="inlineStr">
+      <c r="NB1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_364</t>
         </is>
       </c>
-      <c r="NC1" t="inlineStr">
+      <c r="NC1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_365</t>
         </is>
       </c>
-      <c r="ND1" t="inlineStr">
+      <c r="ND1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_366</t>
         </is>
       </c>
-      <c r="NE1" t="inlineStr">
+      <c r="NE1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_367</t>
         </is>
       </c>
-      <c r="NF1" t="inlineStr">
+      <c r="NF1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_368</t>
         </is>
       </c>
-      <c r="NG1" t="inlineStr">
+      <c r="NG1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_369</t>
         </is>
       </c>
-      <c r="NH1" t="inlineStr">
+      <c r="NH1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_370</t>
         </is>
       </c>
-      <c r="NI1" t="inlineStr">
+      <c r="NI1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_371</t>
         </is>
       </c>
-      <c r="NJ1" t="inlineStr">
+      <c r="NJ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_372</t>
         </is>
       </c>
-      <c r="NK1" t="inlineStr">
+      <c r="NK1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_373</t>
         </is>
       </c>
-      <c r="NL1" t="inlineStr">
+      <c r="NL1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_374</t>
         </is>
       </c>
-      <c r="NM1" t="inlineStr">
+      <c r="NM1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_375</t>
         </is>
       </c>
-      <c r="NN1" t="inlineStr">
+      <c r="NN1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_376</t>
         </is>
       </c>
-      <c r="NO1" t="inlineStr">
+      <c r="NO1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_377</t>
         </is>
       </c>
-      <c r="NP1" t="inlineStr">
+      <c r="NP1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_378</t>
         </is>
       </c>
-      <c r="NQ1" t="inlineStr">
+      <c r="NQ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_379</t>
         </is>
       </c>
-      <c r="NR1" t="inlineStr">
+      <c r="NR1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_380</t>
         </is>
       </c>
-      <c r="NS1" t="inlineStr">
+      <c r="NS1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_381</t>
         </is>
       </c>
-      <c r="NT1" t="inlineStr">
+      <c r="NT1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_382</t>
         </is>
       </c>
-      <c r="NU1" t="inlineStr">
+      <c r="NU1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_383</t>
         </is>
       </c>
-      <c r="NV1" t="inlineStr">
+      <c r="NV1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_384</t>
         </is>
       </c>
-      <c r="NW1" t="inlineStr">
+      <c r="NW1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_385</t>
         </is>
       </c>
-      <c r="NX1" t="inlineStr">
+      <c r="NX1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_386</t>
         </is>
       </c>
-      <c r="NY1" t="inlineStr">
+      <c r="NY1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_387</t>
         </is>
       </c>
-      <c r="NZ1" t="inlineStr">
+      <c r="NZ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_388</t>
         </is>
       </c>
-      <c r="OA1" t="inlineStr">
+      <c r="OA1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_389</t>
         </is>
       </c>
-      <c r="OB1" t="inlineStr">
+      <c r="OB1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_390</t>
         </is>
       </c>
-      <c r="OC1" t="inlineStr">
+      <c r="OC1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_391</t>
         </is>
       </c>
-      <c r="OD1" t="inlineStr">
+      <c r="OD1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_392</t>
         </is>
       </c>
-      <c r="OE1" t="inlineStr">
+      <c r="OE1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_393</t>
         </is>
       </c>
-      <c r="OF1" t="inlineStr">
+      <c r="OF1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_394</t>
         </is>
       </c>
-      <c r="OG1" t="inlineStr">
+      <c r="OG1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_395</t>
         </is>
       </c>
-      <c r="OH1" t="inlineStr">
+      <c r="OH1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_396</t>
         </is>
       </c>
-      <c r="OI1" t="inlineStr">
+      <c r="OI1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_397</t>
         </is>
       </c>
-      <c r="OJ1" t="inlineStr">
+      <c r="OJ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_398</t>
         </is>
       </c>
-      <c r="OK1" t="inlineStr">
+      <c r="OK1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_399</t>
         </is>
       </c>
-      <c r="OL1" t="inlineStr">
+      <c r="OL1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_400</t>
         </is>
       </c>
-      <c r="OM1" t="inlineStr">
+      <c r="OM1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_401</t>
         </is>
       </c>
-      <c r="ON1" t="inlineStr">
+      <c r="ON1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_402</t>
         </is>
       </c>
-      <c r="OO1" t="inlineStr">
+      <c r="OO1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_403</t>
         </is>
       </c>
-      <c r="OP1" t="inlineStr">
+      <c r="OP1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_404</t>
         </is>
       </c>
-      <c r="OQ1" t="inlineStr">
+      <c r="OQ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_405</t>
         </is>
       </c>
-      <c r="OR1" t="inlineStr">
+      <c r="OR1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_406</t>
         </is>
       </c>
-      <c r="OS1" t="inlineStr">
+      <c r="OS1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_407</t>
         </is>
       </c>
-      <c r="OT1" t="inlineStr">
+      <c r="OT1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_408</t>
         </is>
       </c>
-      <c r="OU1" t="inlineStr">
+      <c r="OU1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_409</t>
         </is>
       </c>
-      <c r="OV1" t="inlineStr">
+      <c r="OV1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_410</t>
         </is>
       </c>
-      <c r="OW1" t="inlineStr">
+      <c r="OW1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_411</t>
         </is>
       </c>
-      <c r="OX1" t="inlineStr">
+      <c r="OX1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_412</t>
         </is>
       </c>
-      <c r="OY1" t="inlineStr">
+      <c r="OY1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_413</t>
         </is>
       </c>
-      <c r="OZ1" t="inlineStr">
+      <c r="OZ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_414</t>
         </is>
       </c>
-      <c r="PA1" t="inlineStr">
+      <c r="PA1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_415</t>
         </is>
       </c>
-      <c r="PB1" t="inlineStr">
+      <c r="PB1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_416</t>
         </is>
       </c>
-      <c r="PC1" t="inlineStr">
+      <c r="PC1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_417</t>
         </is>
       </c>
-      <c r="PD1" t="inlineStr">
+      <c r="PD1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_418</t>
         </is>
       </c>
-      <c r="PE1" t="inlineStr">
+      <c r="PE1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_419</t>
         </is>
       </c>
-      <c r="PF1" t="inlineStr">
+      <c r="PF1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_420</t>
         </is>
       </c>
-      <c r="PG1" t="inlineStr">
+      <c r="PG1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_421</t>
         </is>
       </c>
-      <c r="PH1" t="inlineStr">
+      <c r="PH1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_422</t>
         </is>
       </c>
-      <c r="PI1" t="inlineStr">
+      <c r="PI1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_423</t>
         </is>
       </c>
-      <c r="PJ1" t="inlineStr">
+      <c r="PJ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_424</t>
         </is>
       </c>
-      <c r="PK1" t="inlineStr">
+      <c r="PK1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_425</t>
         </is>
       </c>
-      <c r="PL1" t="inlineStr">
+      <c r="PL1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_426</t>
         </is>
       </c>
-      <c r="PM1" t="inlineStr">
+      <c r="PM1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_427</t>
         </is>
       </c>
-      <c r="PN1" t="inlineStr">
+      <c r="PN1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_428</t>
         </is>
       </c>
-      <c r="PO1" t="inlineStr">
+      <c r="PO1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_429</t>
         </is>
       </c>
-      <c r="PP1" t="inlineStr">
+      <c r="PP1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_430</t>
         </is>
       </c>
-      <c r="PQ1" t="inlineStr">
+      <c r="PQ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_431</t>
         </is>
       </c>
-      <c r="PR1" t="inlineStr">
+      <c r="PR1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_432</t>
         </is>
       </c>
-      <c r="PS1" t="inlineStr">
+      <c r="PS1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_433</t>
         </is>
       </c>
-      <c r="PT1" t="inlineStr">
+      <c r="PT1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_434</t>
         </is>
       </c>
-      <c r="PU1" t="inlineStr">
+      <c r="PU1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_435</t>
         </is>
       </c>
-      <c r="PV1" t="inlineStr">
+      <c r="PV1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_436</t>
         </is>
       </c>
-      <c r="PW1" t="inlineStr">
+      <c r="PW1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_437</t>
         </is>
       </c>
-      <c r="PX1" t="inlineStr">
+      <c r="PX1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_438</t>
         </is>
       </c>
-      <c r="PY1" t="inlineStr">
+      <c r="PY1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_439</t>
         </is>
       </c>
-      <c r="PZ1" t="inlineStr">
+      <c r="PZ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_440</t>
         </is>
       </c>
-      <c r="QA1" t="inlineStr">
+      <c r="QA1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_441</t>
         </is>
       </c>
-      <c r="QB1" t="inlineStr">
+      <c r="QB1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_442</t>
         </is>
       </c>
-      <c r="QC1" t="inlineStr">
+      <c r="QC1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_443</t>
         </is>
       </c>
-      <c r="QD1" t="inlineStr">
+      <c r="QD1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_444</t>
         </is>
       </c>
-      <c r="QE1" t="inlineStr">
+      <c r="QE1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_445</t>
         </is>
       </c>
-      <c r="QF1" t="inlineStr">
+      <c r="QF1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_446</t>
         </is>
       </c>
-      <c r="QG1" t="inlineStr">
+      <c r="QG1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_447</t>
         </is>
       </c>
-      <c r="QH1" t="inlineStr">
+      <c r="QH1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_448</t>
         </is>
       </c>
-      <c r="QI1" t="inlineStr">
+      <c r="QI1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_449</t>
         </is>
       </c>
-      <c r="QJ1" t="inlineStr">
+      <c r="QJ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_450</t>
         </is>
       </c>
-      <c r="QK1" t="inlineStr">
+      <c r="QK1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_451</t>
         </is>
       </c>
-      <c r="QL1" t="inlineStr">
+      <c r="QL1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_452</t>
         </is>
       </c>
-      <c r="QM1" t="inlineStr">
+      <c r="QM1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_453</t>
         </is>
       </c>
-      <c r="QN1" t="inlineStr">
+      <c r="QN1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_454</t>
         </is>
       </c>
-      <c r="QO1" t="inlineStr">
+      <c r="QO1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_455</t>
         </is>
       </c>
-      <c r="QP1" t="inlineStr">
+      <c r="QP1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_456</t>
         </is>
       </c>
-      <c r="QQ1" t="inlineStr">
+      <c r="QQ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_457</t>
         </is>
       </c>
-      <c r="QR1" t="inlineStr">
+      <c r="QR1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_458</t>
         </is>
       </c>
-      <c r="QS1" t="inlineStr">
+      <c r="QS1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_459</t>
         </is>
       </c>
-      <c r="QT1" t="inlineStr">
+      <c r="QT1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_460</t>
         </is>
       </c>
-      <c r="QU1" t="inlineStr">
+      <c r="QU1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_461</t>
         </is>
       </c>
-      <c r="QV1" t="inlineStr">
+      <c r="QV1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_462</t>
         </is>
       </c>
-      <c r="QW1" t="inlineStr">
+      <c r="QW1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_463</t>
         </is>
       </c>
-      <c r="QX1" t="inlineStr">
+      <c r="QX1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_464</t>
         </is>
       </c>
-      <c r="QY1" t="inlineStr">
+      <c r="QY1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_465</t>
         </is>
       </c>
-      <c r="QZ1" t="inlineStr">
+      <c r="QZ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_466</t>
         </is>
       </c>
-      <c r="RA1" t="inlineStr">
+      <c r="RA1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_467</t>
         </is>
       </c>
-      <c r="RB1" t="inlineStr">
+      <c r="RB1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_468</t>
         </is>
       </c>
-      <c r="RC1" t="inlineStr">
+      <c r="RC1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_469</t>
         </is>
       </c>
-      <c r="RD1" t="inlineStr">
+      <c r="RD1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_470</t>
         </is>
       </c>
-      <c r="RE1" t="inlineStr">
+      <c r="RE1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_471</t>
         </is>
       </c>
-      <c r="RF1" t="inlineStr">
+      <c r="RF1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_472</t>
         </is>
       </c>
-      <c r="RG1" t="inlineStr">
+      <c r="RG1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_473</t>
         </is>
       </c>
-      <c r="RH1" t="inlineStr">
+      <c r="RH1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_474</t>
         </is>
       </c>
-      <c r="RI1" t="inlineStr">
+      <c r="RI1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_475</t>
         </is>
       </c>
-      <c r="RJ1" t="inlineStr">
+      <c r="RJ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_476</t>
         </is>
       </c>
-      <c r="RK1" t="inlineStr">
+      <c r="RK1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_477</t>
         </is>
       </c>
-      <c r="RL1" t="inlineStr">
+      <c r="RL1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_478</t>
         </is>
       </c>
-      <c r="RM1" t="inlineStr">
+      <c r="RM1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_479</t>
         </is>
       </c>
-      <c r="RN1" t="inlineStr">
+      <c r="RN1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_480</t>
         </is>
       </c>
-      <c r="RO1" t="inlineStr">
+      <c r="RO1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_481</t>
         </is>
       </c>
-      <c r="RP1" t="inlineStr">
+      <c r="RP1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_482</t>
         </is>
       </c>
-      <c r="RQ1" t="inlineStr">
+      <c r="RQ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_483</t>
         </is>
       </c>
-      <c r="RR1" t="inlineStr">
+      <c r="RR1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_484</t>
         </is>
       </c>
-      <c r="RS1" t="inlineStr">
+      <c r="RS1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_485</t>
         </is>
       </c>
-      <c r="RT1" t="inlineStr">
+      <c r="RT1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_486</t>
         </is>
       </c>
-      <c r="RU1" t="inlineStr">
+      <c r="RU1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_487</t>
         </is>
       </c>
-      <c r="RV1" t="inlineStr">
+      <c r="RV1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_488</t>
         </is>
       </c>
-      <c r="RW1" t="inlineStr">
+      <c r="RW1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_489</t>
         </is>
       </c>
-      <c r="RX1" t="inlineStr">
+      <c r="RX1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_490</t>
         </is>
       </c>
-      <c r="RY1" t="inlineStr">
+      <c r="RY1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_491</t>
         </is>
       </c>
-      <c r="RZ1" t="inlineStr">
+      <c r="RZ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_492</t>
         </is>
       </c>
-      <c r="SA1" t="inlineStr">
+      <c r="SA1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_493</t>
         </is>
       </c>
-      <c r="SB1" t="inlineStr">
+      <c r="SB1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_494</t>
         </is>
       </c>
-      <c r="SC1" t="inlineStr">
+      <c r="SC1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_495</t>
         </is>
       </c>
-      <c r="SD1" t="inlineStr">
+      <c r="SD1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_496</t>
         </is>
       </c>
-      <c r="SE1" t="inlineStr">
+      <c r="SE1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_497</t>
         </is>
       </c>
-      <c r="SF1" t="inlineStr">
+      <c r="SF1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_498</t>
         </is>
       </c>
-      <c r="SG1" t="inlineStr">
+      <c r="SG1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_499</t>
         </is>
       </c>
-      <c r="SH1" t="inlineStr">
+      <c r="SH1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_500</t>
         </is>
       </c>
-      <c r="SI1" t="inlineStr">
+      <c r="SI1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_501</t>
         </is>
       </c>
-      <c r="SJ1" t="inlineStr">
+      <c r="SJ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_502</t>
         </is>
       </c>
-      <c r="SK1" t="inlineStr">
+      <c r="SK1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_503</t>
         </is>
       </c>
-      <c r="SL1" t="inlineStr">
+      <c r="SL1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_504</t>
         </is>
       </c>
-      <c r="SM1" t="inlineStr">
+      <c r="SM1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_505</t>
         </is>
       </c>
-      <c r="SN1" t="inlineStr">
+      <c r="SN1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_506</t>
         </is>
       </c>
-      <c r="SO1" t="inlineStr">
+      <c r="SO1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_507</t>
         </is>
       </c>
-      <c r="SP1" t="inlineStr">
+      <c r="SP1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_508</t>
         </is>
       </c>
-      <c r="SQ1" t="inlineStr">
+      <c r="SQ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_509</t>
         </is>
       </c>
-      <c r="SR1" t="inlineStr">
+      <c r="SR1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_510</t>
         </is>
       </c>
-      <c r="SS1" t="inlineStr">
+      <c r="SS1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_511</t>
         </is>
       </c>
-      <c r="ST1" t="inlineStr">
+      <c r="ST1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_512</t>
         </is>
       </c>
-      <c r="SU1" t="inlineStr">
+      <c r="SU1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_513</t>
         </is>
       </c>
-      <c r="SV1" t="inlineStr">
+      <c r="SV1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_514</t>
         </is>
       </c>
-      <c r="SW1" t="inlineStr">
+      <c r="SW1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_515</t>
         </is>
       </c>
-      <c r="SX1" t="inlineStr">
+      <c r="SX1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_516</t>
         </is>
       </c>
-      <c r="SY1" t="inlineStr">
+      <c r="SY1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_517</t>
         </is>
       </c>
-      <c r="SZ1" t="inlineStr">
+      <c r="SZ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_518</t>
         </is>
       </c>
-      <c r="TA1" t="inlineStr">
+      <c r="TA1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_519</t>
         </is>
       </c>
-      <c r="TB1" t="inlineStr">
+      <c r="TB1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_520</t>
         </is>
       </c>
-      <c r="TC1" t="inlineStr">
+      <c r="TC1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_521</t>
         </is>
       </c>
-      <c r="TD1" t="inlineStr">
+      <c r="TD1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_522</t>
         </is>
       </c>
-      <c r="TE1" t="inlineStr">
+      <c r="TE1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_523</t>
         </is>
       </c>
-      <c r="TF1" t="inlineStr">
+      <c r="TF1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_524</t>
         </is>
       </c>
-      <c r="TG1" t="inlineStr">
+      <c r="TG1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_525</t>
         </is>
       </c>
-      <c r="TH1" t="inlineStr">
+      <c r="TH1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_526</t>
         </is>
       </c>
-      <c r="TI1" t="inlineStr">
+      <c r="TI1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_527</t>
         </is>
       </c>
-      <c r="TJ1" t="inlineStr">
+      <c r="TJ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_528</t>
         </is>
       </c>
-      <c r="TK1" t="inlineStr">
+      <c r="TK1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_529</t>
         </is>
       </c>
-      <c r="TL1" t="inlineStr">
+      <c r="TL1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_530</t>
         </is>
       </c>
-      <c r="TM1" t="inlineStr">
+      <c r="TM1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_531</t>
         </is>
       </c>
-      <c r="TN1" t="inlineStr">
+      <c r="TN1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_532</t>
         </is>
       </c>
-      <c r="TO1" t="inlineStr">
+      <c r="TO1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_533</t>
         </is>
       </c>
-      <c r="TP1" t="inlineStr">
+      <c r="TP1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_534</t>
         </is>
       </c>
-      <c r="TQ1" t="inlineStr">
+      <c r="TQ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_535</t>
         </is>
       </c>
-      <c r="TR1" t="inlineStr">
+      <c r="TR1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_536</t>
         </is>
       </c>
-      <c r="TS1" t="inlineStr">
+      <c r="TS1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_537</t>
         </is>
       </c>
-      <c r="TT1" t="inlineStr">
+      <c r="TT1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_538</t>
         </is>
       </c>
-      <c r="TU1" t="inlineStr">
+      <c r="TU1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_539</t>
         </is>
       </c>
-      <c r="TV1" t="inlineStr">
+      <c r="TV1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_540</t>
         </is>
       </c>
-      <c r="TW1" t="inlineStr">
+      <c r="TW1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_541</t>
         </is>
       </c>
-      <c r="TX1" t="inlineStr">
+      <c r="TX1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_542</t>
         </is>
       </c>
-      <c r="TY1" t="inlineStr">
+      <c r="TY1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_543</t>
         </is>
       </c>
-      <c r="TZ1" t="inlineStr">
+      <c r="TZ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_544</t>
         </is>
       </c>
-      <c r="UA1" t="inlineStr">
+      <c r="UA1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_545</t>
         </is>
       </c>
-      <c r="UB1" t="inlineStr">
+      <c r="UB1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_546</t>
         </is>
       </c>
-      <c r="UC1" t="inlineStr">
+      <c r="UC1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_547</t>
         </is>
       </c>
-      <c r="UD1" t="inlineStr">
+      <c r="UD1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_548</t>
         </is>
       </c>
-      <c r="UE1" t="inlineStr">
+      <c r="UE1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_549</t>
         </is>
       </c>
-      <c r="UF1" t="inlineStr">
+      <c r="UF1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_550</t>
         </is>
       </c>
-      <c r="UG1" t="inlineStr">
+      <c r="UG1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_551</t>
         </is>
       </c>
-      <c r="UH1" t="inlineStr">
+      <c r="UH1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_552</t>
         </is>
       </c>
-      <c r="UI1" t="inlineStr">
+      <c r="UI1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_553</t>
         </is>
       </c>
-      <c r="UJ1" t="inlineStr">
+      <c r="UJ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_554</t>
         </is>
       </c>
-      <c r="UK1" t="inlineStr">
+      <c r="UK1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_555</t>
         </is>
       </c>
-      <c r="UL1" t="inlineStr">
+      <c r="UL1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_556</t>
         </is>
       </c>
-      <c r="UM1" t="inlineStr">
+      <c r="UM1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_557</t>
         </is>
       </c>
-      <c r="UN1" t="inlineStr">
+      <c r="UN1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_558</t>
         </is>
       </c>
-      <c r="UO1" t="inlineStr">
+      <c r="UO1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_559</t>
         </is>
       </c>
-      <c r="UP1" t="inlineStr">
+      <c r="UP1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_560</t>
         </is>
       </c>
-      <c r="UQ1" t="inlineStr">
+      <c r="UQ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_561</t>
         </is>
       </c>
-      <c r="UR1" t="inlineStr">
+      <c r="UR1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_562</t>
         </is>
       </c>
-      <c r="US1" t="inlineStr">
+      <c r="US1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_563</t>
         </is>
       </c>
-      <c r="UT1" t="inlineStr">
+      <c r="UT1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_564</t>
         </is>
       </c>
-      <c r="UU1" t="inlineStr">
+      <c r="UU1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_565</t>
         </is>
       </c>
-      <c r="UV1" t="inlineStr">
+      <c r="UV1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_566</t>
         </is>
       </c>
-      <c r="UW1" t="inlineStr">
+      <c r="UW1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_567</t>
         </is>
       </c>
-      <c r="UX1" t="inlineStr">
+      <c r="UX1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_568</t>
         </is>
       </c>
-      <c r="UY1" t="inlineStr">
+      <c r="UY1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_569</t>
         </is>
       </c>
-      <c r="UZ1" t="inlineStr">
+      <c r="UZ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_570</t>
         </is>
       </c>
-      <c r="VA1" t="inlineStr">
+      <c r="VA1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_571</t>
         </is>
       </c>
-      <c r="VB1" t="inlineStr">
+      <c r="VB1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_572</t>
         </is>
       </c>
-      <c r="VC1" t="inlineStr">
+      <c r="VC1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_573</t>
         </is>
       </c>
-      <c r="VD1" t="inlineStr">
+      <c r="VD1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_574</t>
         </is>
       </c>
-      <c r="VE1" t="inlineStr">
+      <c r="VE1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_575</t>
         </is>
       </c>
-      <c r="VF1" t="inlineStr">
+      <c r="VF1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_576</t>
         </is>
       </c>
-      <c r="VG1" t="inlineStr">
+      <c r="VG1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_577</t>
         </is>
       </c>
-      <c r="VH1" t="inlineStr">
+      <c r="VH1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_578</t>
         </is>
       </c>
-      <c r="VI1" t="inlineStr">
+      <c r="VI1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_579</t>
         </is>
       </c>
-      <c r="VJ1" t="inlineStr">
+      <c r="VJ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_580</t>
         </is>
       </c>
-      <c r="VK1" t="inlineStr">
+      <c r="VK1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_581</t>
         </is>
       </c>
-      <c r="VL1" t="inlineStr">
+      <c r="VL1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_582</t>
         </is>
       </c>
-      <c r="VM1" t="inlineStr">
+      <c r="VM1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_583</t>
         </is>
       </c>
-      <c r="VN1" t="inlineStr">
+      <c r="VN1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_584</t>
         </is>
       </c>
-      <c r="VO1" t="inlineStr">
+      <c r="VO1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_585</t>
         </is>
       </c>
-      <c r="VP1" t="inlineStr">
+      <c r="VP1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_586</t>
         </is>
       </c>
-      <c r="VQ1" t="inlineStr">
+      <c r="VQ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_587</t>
         </is>
       </c>
-      <c r="VR1" t="inlineStr">
+      <c r="VR1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_588</t>
         </is>
       </c>
-      <c r="VS1" t="inlineStr">
+      <c r="VS1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_589</t>
         </is>
       </c>
-      <c r="VT1" t="inlineStr">
+      <c r="VT1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_590</t>
         </is>
       </c>
-      <c r="VU1" t="inlineStr">
+      <c r="VU1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_591</t>
         </is>
       </c>
-      <c r="VV1" t="inlineStr">
+      <c r="VV1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_592</t>
         </is>
       </c>
-      <c r="VW1" t="inlineStr">
+      <c r="VW1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_593</t>
         </is>
       </c>
-      <c r="VX1" t="inlineStr">
+      <c r="VX1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_594</t>
         </is>
       </c>
-      <c r="VY1" t="inlineStr">
+      <c r="VY1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_595</t>
         </is>
       </c>
-      <c r="VZ1" t="inlineStr">
+      <c r="VZ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_596</t>
         </is>
       </c>
-      <c r="WA1" t="inlineStr">
+      <c r="WA1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_597</t>
         </is>
       </c>
-      <c r="WB1" t="inlineStr">
+      <c r="WB1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_598</t>
         </is>
       </c>
-      <c r="WC1" t="inlineStr">
+      <c r="WC1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_599</t>
         </is>
       </c>
-      <c r="WD1" t="inlineStr">
+      <c r="WD1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_600</t>
         </is>
       </c>
-      <c r="WE1" t="inlineStr">
+      <c r="WE1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_601</t>
         </is>
       </c>
-      <c r="WF1" t="inlineStr">
+      <c r="WF1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_602</t>
         </is>
       </c>
-      <c r="WG1" t="inlineStr">
+      <c r="WG1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_603</t>
         </is>
       </c>
-      <c r="WH1" t="inlineStr">
+      <c r="WH1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_604</t>
         </is>
       </c>
-      <c r="WI1" t="inlineStr">
+      <c r="WI1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_605</t>
         </is>
       </c>
-      <c r="WJ1" t="inlineStr">
+      <c r="WJ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_606</t>
         </is>
       </c>
-      <c r="WK1" t="inlineStr">
+      <c r="WK1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_607</t>
         </is>
       </c>
-      <c r="WL1" t="inlineStr">
+      <c r="WL1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_608</t>
         </is>
       </c>
-      <c r="WM1" t="inlineStr">
+      <c r="WM1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_609</t>
         </is>
       </c>
-      <c r="WN1" t="inlineStr">
+      <c r="WN1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_610</t>
         </is>
       </c>
-      <c r="WO1" t="inlineStr">
+      <c r="WO1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_611</t>
         </is>
       </c>
-      <c r="WP1" t="inlineStr">
+      <c r="WP1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_612</t>
         </is>
       </c>
-      <c r="WQ1" t="inlineStr">
+      <c r="WQ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_613</t>
         </is>
       </c>
-      <c r="WR1" t="inlineStr">
+      <c r="WR1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_614</t>
         </is>
       </c>
-      <c r="WS1" t="inlineStr">
+      <c r="WS1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_615</t>
         </is>
       </c>
-      <c r="WT1" t="inlineStr">
+      <c r="WT1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_616</t>
         </is>
       </c>
-      <c r="WU1" t="inlineStr">
+      <c r="WU1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_617</t>
         </is>
       </c>
-      <c r="WV1" t="inlineStr">
+      <c r="WV1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_618</t>
         </is>
       </c>
-      <c r="WW1" t="inlineStr">
+      <c r="WW1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_619</t>
         </is>
       </c>
-      <c r="WX1" t="inlineStr">
+      <c r="WX1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_620</t>
         </is>
       </c>
-      <c r="WY1" t="inlineStr">
+      <c r="WY1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_621</t>
         </is>
       </c>
-      <c r="WZ1" t="inlineStr">
+      <c r="WZ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_622</t>
         </is>
       </c>
-      <c r="XA1" t="inlineStr">
+      <c r="XA1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_623</t>
         </is>
       </c>
-      <c r="XB1" t="inlineStr">
+      <c r="XB1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_624</t>
         </is>
       </c>
-      <c r="XC1" t="inlineStr">
+      <c r="XC1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_625</t>
         </is>
       </c>
-      <c r="XD1" t="inlineStr">
+      <c r="XD1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_626</t>
         </is>
       </c>
-      <c r="XE1" t="inlineStr">
+      <c r="XE1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_627</t>
         </is>
       </c>
-      <c r="XF1" t="inlineStr">
+      <c r="XF1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_628</t>
         </is>
       </c>
-      <c r="XG1" t="inlineStr">
+      <c r="XG1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_629</t>
         </is>
       </c>
-      <c r="XH1" t="inlineStr">
+      <c r="XH1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_630</t>
         </is>
       </c>
-      <c r="XI1" t="inlineStr">
+      <c r="XI1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_631</t>
         </is>
       </c>
-      <c r="XJ1" t="inlineStr">
+      <c r="XJ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_632</t>
         </is>
       </c>
-      <c r="XK1" t="inlineStr">
+      <c r="XK1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_633</t>
         </is>
       </c>
-      <c r="XL1" t="inlineStr">
+      <c r="XL1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_634</t>
         </is>
       </c>
-      <c r="XM1" t="inlineStr">
+      <c r="XM1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_635</t>
         </is>
       </c>
-      <c r="XN1" t="inlineStr">
+      <c r="XN1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_636</t>
         </is>
       </c>
-      <c r="XO1" t="inlineStr">
+      <c r="XO1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_637</t>
         </is>
       </c>
-      <c r="XP1" t="inlineStr">
+      <c r="XP1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_638</t>
         </is>
       </c>
-      <c r="XQ1" t="inlineStr">
+      <c r="XQ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_639</t>
         </is>
       </c>
-      <c r="XR1" t="inlineStr">
+      <c r="XR1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_640</t>
         </is>
       </c>
-      <c r="XS1" t="inlineStr">
+      <c r="XS1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_641</t>
         </is>
       </c>
-      <c r="XT1" t="inlineStr">
+      <c r="XT1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_642</t>
         </is>
       </c>
-      <c r="XU1" t="inlineStr">
+      <c r="XU1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_643</t>
         </is>
       </c>
-      <c r="XV1" t="inlineStr">
+      <c r="XV1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_644</t>
         </is>
       </c>
-      <c r="XW1" t="inlineStr">
+      <c r="XW1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_645</t>
         </is>
       </c>
-      <c r="XX1" t="inlineStr">
+      <c r="XX1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_646</t>
         </is>
       </c>
-      <c r="XY1" t="inlineStr">
+      <c r="XY1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_647</t>
         </is>
       </c>
-      <c r="XZ1" t="inlineStr">
+      <c r="XZ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_648</t>
         </is>
       </c>
-      <c r="YA1" t="inlineStr">
+      <c r="YA1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_649</t>
         </is>
       </c>
-      <c r="YB1" t="inlineStr">
+      <c r="YB1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_650</t>
         </is>
       </c>
-      <c r="YC1" t="inlineStr">
+      <c r="YC1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_651</t>
         </is>
       </c>
-      <c r="YD1" t="inlineStr">
+      <c r="YD1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_652</t>
         </is>
       </c>
-      <c r="YE1" t="inlineStr">
+      <c r="YE1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_653</t>
         </is>
       </c>
-      <c r="YF1" t="inlineStr">
+      <c r="YF1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_654</t>
         </is>
       </c>
-      <c r="YG1" t="inlineStr">
+      <c r="YG1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_655</t>
         </is>
       </c>
-      <c r="YH1" t="inlineStr">
+      <c r="YH1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_656</t>
         </is>
       </c>
-      <c r="YI1" t="inlineStr">
+      <c r="YI1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_657</t>
         </is>
       </c>
-      <c r="YJ1" t="inlineStr">
+      <c r="YJ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_658</t>
         </is>
       </c>
-      <c r="YK1" t="inlineStr">
+      <c r="YK1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_659</t>
         </is>
       </c>
-      <c r="YL1" t="inlineStr">
+      <c r="YL1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_660</t>
         </is>
       </c>
-      <c r="YM1" t="inlineStr">
+      <c r="YM1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_661</t>
         </is>
       </c>
-      <c r="YN1" t="inlineStr">
+      <c r="YN1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_662</t>
         </is>
       </c>
-      <c r="YO1" t="inlineStr">
+      <c r="YO1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_663</t>
         </is>
       </c>
-      <c r="YP1" t="inlineStr">
+      <c r="YP1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_664</t>
         </is>
       </c>
-      <c r="YQ1" t="inlineStr">
+      <c r="YQ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_665</t>
         </is>
       </c>
-      <c r="YR1" t="inlineStr">
+      <c r="YR1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_666</t>
         </is>
       </c>
-      <c r="YS1" t="inlineStr">
+      <c r="YS1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_667</t>
         </is>
       </c>
-      <c r="YT1" t="inlineStr">
+      <c r="YT1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_668</t>
         </is>
       </c>
-      <c r="YU1" t="inlineStr">
+      <c r="YU1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_669</t>
         </is>
       </c>
-      <c r="YV1" t="inlineStr">
+      <c r="YV1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_670</t>
         </is>
       </c>
-      <c r="YW1" t="inlineStr">
+      <c r="YW1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_671</t>
         </is>
       </c>
-      <c r="YX1" t="inlineStr">
+      <c r="YX1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_672</t>
         </is>
       </c>
-      <c r="YY1" t="inlineStr">
+      <c r="YY1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_673</t>
         </is>
       </c>
-      <c r="YZ1" t="inlineStr">
+      <c r="YZ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_674</t>
         </is>
       </c>
-      <c r="ZA1" t="inlineStr">
+      <c r="ZA1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_675</t>
         </is>
       </c>
-      <c r="ZB1" t="inlineStr">
+      <c r="ZB1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_676</t>
         </is>
       </c>
-      <c r="ZC1" t="inlineStr">
+      <c r="ZC1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_677</t>
         </is>
       </c>
-      <c r="ZD1" t="inlineStr">
+      <c r="ZD1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_678</t>
         </is>
       </c>
-      <c r="ZE1" t="inlineStr">
+      <c r="ZE1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_679</t>
         </is>
       </c>
-      <c r="ZF1" t="inlineStr">
+      <c r="ZF1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_680</t>
         </is>
       </c>
-      <c r="ZG1" t="inlineStr">
+      <c r="ZG1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_681</t>
         </is>
       </c>
-      <c r="ZH1" t="inlineStr">
+      <c r="ZH1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_682</t>
         </is>
       </c>
-      <c r="ZI1" t="inlineStr">
+      <c r="ZI1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_683</t>
         </is>
       </c>
-      <c r="ZJ1" t="inlineStr">
+      <c r="ZJ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_684</t>
         </is>
       </c>
-      <c r="ZK1" t="inlineStr">
+      <c r="ZK1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_685</t>
         </is>
       </c>
-      <c r="ZL1" t="inlineStr">
+      <c r="ZL1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_686</t>
         </is>
       </c>
-      <c r="ZM1" t="inlineStr">
+      <c r="ZM1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_687</t>
         </is>
       </c>
-      <c r="ZN1" t="inlineStr">
+      <c r="ZN1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_688</t>
         </is>
       </c>
-      <c r="ZO1" t="inlineStr">
+      <c r="ZO1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_689</t>
         </is>
       </c>
-      <c r="ZP1" t="inlineStr">
+      <c r="ZP1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_690</t>
         </is>
       </c>
-      <c r="ZQ1" t="inlineStr">
+      <c r="ZQ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_691</t>
         </is>
       </c>
-      <c r="ZR1" t="inlineStr">
+      <c r="ZR1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_692</t>
         </is>
       </c>
-      <c r="ZS1" t="inlineStr">
+      <c r="ZS1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_693</t>
         </is>
       </c>
-      <c r="ZT1" t="inlineStr">
+      <c r="ZT1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_694</t>
         </is>
       </c>
-      <c r="ZU1" t="inlineStr">
+      <c r="ZU1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_695</t>
         </is>
       </c>
-      <c r="ZV1" t="inlineStr">
+      <c r="ZV1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_696</t>
         </is>
       </c>
-      <c r="ZW1" t="inlineStr">
+      <c r="ZW1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_697</t>
         </is>
       </c>
-      <c r="ZX1" t="inlineStr">
+      <c r="ZX1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_698</t>
         </is>
       </c>
-      <c r="ZY1" t="inlineStr">
+      <c r="ZY1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_699</t>
         </is>
       </c>
-      <c r="ZZ1" t="inlineStr">
+      <c r="ZZ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_700</t>
         </is>
       </c>
-      <c r="AAA1" t="inlineStr">
+      <c r="AAA1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_701</t>
         </is>
       </c>
-      <c r="AAB1" t="inlineStr">
+      <c r="AAB1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_702</t>
         </is>
       </c>
-      <c r="AAC1" t="inlineStr">
+      <c r="AAC1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_703</t>
         </is>
       </c>
-      <c r="AAD1" t="inlineStr">
+      <c r="AAD1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_704</t>
         </is>
       </c>
-      <c r="AAE1" t="inlineStr">
+      <c r="AAE1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_705</t>
         </is>
       </c>
-      <c r="AAF1" t="inlineStr">
+      <c r="AAF1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_706</t>
         </is>
       </c>
-      <c r="AAG1" t="inlineStr">
+      <c r="AAG1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_707</t>
         </is>
       </c>
-      <c r="AAH1" t="inlineStr">
+      <c r="AAH1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_708</t>
         </is>
       </c>
-      <c r="AAI1" t="inlineStr">
+      <c r="AAI1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_709</t>
         </is>
       </c>
-      <c r="AAJ1" t="inlineStr">
+      <c r="AAJ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_710</t>
         </is>
       </c>
-      <c r="AAK1" t="inlineStr">
+      <c r="AAK1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_711</t>
         </is>
       </c>
-      <c r="AAL1" t="inlineStr">
+      <c r="AAL1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_712</t>
         </is>
       </c>
-      <c r="AAM1" t="inlineStr">
+      <c r="AAM1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_713</t>
         </is>
       </c>
-      <c r="AAN1" t="inlineStr">
+      <c r="AAN1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_714</t>
         </is>
       </c>
-      <c r="AAO1" t="inlineStr">
+      <c r="AAO1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_715</t>
         </is>
       </c>
-      <c r="AAP1" t="inlineStr">
+      <c r="AAP1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_716</t>
         </is>
       </c>
-      <c r="AAQ1" t="inlineStr">
+      <c r="AAQ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_717</t>
         </is>
       </c>
-      <c r="AAR1" t="inlineStr">
+      <c r="AAR1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_718</t>
         </is>
       </c>
-      <c r="AAS1" t="inlineStr">
+      <c r="AAS1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_719</t>
         </is>
       </c>
-      <c r="AAT1" t="inlineStr">
+      <c r="AAT1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_720</t>
         </is>
       </c>
-      <c r="AAU1" t="inlineStr">
+      <c r="AAU1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_721</t>
         </is>
       </c>
-      <c r="AAV1" t="inlineStr">
+      <c r="AAV1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_722</t>
         </is>
       </c>
-      <c r="AAW1" t="inlineStr">
+      <c r="AAW1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_723</t>
         </is>
       </c>
-      <c r="AAX1" t="inlineStr">
+      <c r="AAX1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_724</t>
         </is>
       </c>
-      <c r="AAY1" t="inlineStr">
+      <c r="AAY1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_725</t>
         </is>
       </c>
-      <c r="AAZ1" t="inlineStr">
+      <c r="AAZ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_726</t>
         </is>
       </c>
-      <c r="ABA1" t="inlineStr">
+      <c r="ABA1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_727</t>
         </is>
       </c>
-      <c r="ABB1" t="inlineStr">
+      <c r="ABB1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_728</t>
         </is>
       </c>
-      <c r="ABC1" t="inlineStr">
+      <c r="ABC1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_729</t>
         </is>
       </c>
-      <c r="ABD1" t="inlineStr">
+      <c r="ABD1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_730</t>
         </is>
       </c>
-      <c r="ABE1" t="inlineStr">
+      <c r="ABE1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_731</t>
         </is>
       </c>
-      <c r="ABF1" t="inlineStr">
+      <c r="ABF1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_732</t>
         </is>
       </c>
-      <c r="ABG1" t="inlineStr">
+      <c r="ABG1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_733</t>
         </is>
       </c>
-      <c r="ABH1" t="inlineStr">
+      <c r="ABH1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_734</t>
         </is>
       </c>
-      <c r="ABI1" t="inlineStr">
+      <c r="ABI1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_735</t>
         </is>
       </c>
-      <c r="ABJ1" t="inlineStr">
+      <c r="ABJ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_736</t>
         </is>
       </c>
-      <c r="ABK1" t="inlineStr">
+      <c r="ABK1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_737</t>
         </is>
       </c>
-      <c r="ABL1" t="inlineStr">
+      <c r="ABL1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_738</t>
         </is>
       </c>
-      <c r="ABM1" t="inlineStr">
+      <c r="ABM1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_739</t>
         </is>
       </c>
-      <c r="ABN1" t="inlineStr">
+      <c r="ABN1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_740</t>
         </is>
       </c>
-      <c r="ABO1" t="inlineStr">
+      <c r="ABO1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_741</t>
         </is>
       </c>
-      <c r="ABP1" t="inlineStr">
+      <c r="ABP1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_742</t>
         </is>
       </c>
-      <c r="ABQ1" t="inlineStr">
+      <c r="ABQ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_743</t>
         </is>
       </c>
-      <c r="ABR1" t="inlineStr">
+      <c r="ABR1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_744</t>
         </is>
       </c>
-      <c r="ABS1" t="inlineStr">
+      <c r="ABS1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_745</t>
         </is>
       </c>
-      <c r="ABT1" t="inlineStr">
+      <c r="ABT1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_746</t>
         </is>
       </c>
-      <c r="ABU1" t="inlineStr">
+      <c r="ABU1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_747</t>
         </is>
       </c>
-      <c r="ABV1" t="inlineStr">
+      <c r="ABV1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_748</t>
         </is>
       </c>
-      <c r="ABW1" t="inlineStr">
+      <c r="ABW1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_749</t>
         </is>
       </c>
-      <c r="ABX1" t="inlineStr">
+      <c r="ABX1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_750</t>
         </is>
       </c>
-      <c r="ABY1" t="inlineStr">
+      <c r="ABY1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_751</t>
         </is>
       </c>
-      <c r="ABZ1" t="inlineStr">
+      <c r="ABZ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_752</t>
         </is>
       </c>
-      <c r="ACA1" t="inlineStr">
+      <c r="ACA1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_753</t>
         </is>
       </c>
-      <c r="ACB1" t="inlineStr">
+      <c r="ACB1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_754</t>
         </is>
       </c>
-      <c r="ACC1" t="inlineStr">
+      <c r="ACC1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_755</t>
         </is>
       </c>
-      <c r="ACD1" t="inlineStr">
+      <c r="ACD1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_756</t>
         </is>
       </c>
-      <c r="ACE1" t="inlineStr">
+      <c r="ACE1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_757</t>
         </is>
       </c>
-      <c r="ACF1" t="inlineStr">
+      <c r="ACF1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_758</t>
         </is>
       </c>
-      <c r="ACG1" t="inlineStr">
+      <c r="ACG1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_759</t>
         </is>
       </c>
-      <c r="ACH1" t="inlineStr">
+      <c r="ACH1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_760</t>
         </is>
       </c>
-      <c r="ACI1" t="inlineStr">
+      <c r="ACI1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_761</t>
         </is>
       </c>
-      <c r="ACJ1" t="inlineStr">
+      <c r="ACJ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_762</t>
         </is>
       </c>
-      <c r="ACK1" t="inlineStr">
+      <c r="ACK1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_763</t>
         </is>
       </c>
-      <c r="ACL1" t="inlineStr">
+      <c r="ACL1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_764</t>
         </is>
       </c>
-      <c r="ACM1" t="inlineStr">
+      <c r="ACM1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_765</t>
         </is>
       </c>
-      <c r="ACN1" t="inlineStr">
+      <c r="ACN1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_766</t>
         </is>
       </c>
-      <c r="ACO1" t="inlineStr">
+      <c r="ACO1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_767</t>
         </is>
       </c>
-      <c r="ACP1" t="inlineStr">
+      <c r="ACP1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_768</t>
         </is>
       </c>
-      <c r="ACQ1" t="inlineStr">
+      <c r="ACQ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_769</t>
         </is>
       </c>
-      <c r="ACR1" t="inlineStr">
+      <c r="ACR1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_770</t>
         </is>
       </c>
-      <c r="ACS1" t="inlineStr">
+      <c r="ACS1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_771</t>
         </is>
       </c>
-      <c r="ACT1" t="inlineStr">
+      <c r="ACT1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_772</t>
         </is>
       </c>
-      <c r="ACU1" t="inlineStr">
+      <c r="ACU1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_773</t>
         </is>
       </c>
-      <c r="ACV1" t="inlineStr">
+      <c r="ACV1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_774</t>
         </is>
       </c>
-      <c r="ACW1" t="inlineStr">
+      <c r="ACW1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_775</t>
         </is>
       </c>
-      <c r="ACX1" t="inlineStr">
+      <c r="ACX1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_776</t>
         </is>
       </c>
-      <c r="ACY1" t="inlineStr">
+      <c r="ACY1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_777</t>
         </is>
       </c>
-      <c r="ACZ1" t="inlineStr">
+      <c r="ACZ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_778</t>
         </is>
       </c>
-      <c r="ADA1" t="inlineStr">
+      <c r="ADA1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_779</t>
         </is>
       </c>
-      <c r="ADB1" t="inlineStr">
+      <c r="ADB1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_780</t>
         </is>
       </c>
-      <c r="ADC1" t="inlineStr">
+      <c r="ADC1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_781</t>
         </is>
       </c>
-      <c r="ADD1" t="inlineStr">
+      <c r="ADD1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_782</t>
         </is>
       </c>
-      <c r="ADE1" t="inlineStr">
+      <c r="ADE1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_783</t>
         </is>
       </c>
-      <c r="ADF1" t="inlineStr">
+      <c r="ADF1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_784</t>
         </is>
       </c>
-      <c r="ADG1" t="inlineStr">
+      <c r="ADG1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_785</t>
         </is>
       </c>
-      <c r="ADH1" t="inlineStr">
+      <c r="ADH1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_786</t>
         </is>
       </c>
-      <c r="ADI1" t="inlineStr">
+      <c r="ADI1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_787</t>
         </is>
       </c>
-      <c r="ADJ1" t="inlineStr">
+      <c r="ADJ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_788</t>
         </is>
       </c>
-      <c r="ADK1" t="inlineStr">
+      <c r="ADK1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_789</t>
         </is>
       </c>
-      <c r="ADL1" t="inlineStr">
+      <c r="ADL1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_790</t>
         </is>
       </c>
-      <c r="ADM1" t="inlineStr">
+      <c r="ADM1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_791</t>
         </is>
       </c>
-      <c r="ADN1" t="inlineStr">
+      <c r="ADN1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_792</t>
         </is>
       </c>
-      <c r="ADO1" t="inlineStr">
+      <c r="ADO1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_793</t>
         </is>
       </c>
-      <c r="ADP1" t="inlineStr">
+      <c r="ADP1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_794</t>
         </is>
       </c>
-      <c r="ADQ1" t="inlineStr">
+      <c r="ADQ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_795</t>
         </is>
       </c>
-      <c r="ADR1" t="inlineStr">
+      <c r="ADR1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_796</t>
         </is>
       </c>
-      <c r="ADS1" t="inlineStr">
+      <c r="ADS1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_797</t>
         </is>
       </c>
-      <c r="ADT1" t="inlineStr">
+      <c r="ADT1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_798</t>
         </is>
       </c>
-      <c r="ADU1" t="inlineStr">
+      <c r="ADU1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_799</t>
         </is>
       </c>
-      <c r="ADV1" t="inlineStr">
+      <c r="ADV1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_800</t>
         </is>
       </c>
-      <c r="ADW1" t="inlineStr">
+      <c r="ADW1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_801</t>
         </is>
       </c>
-      <c r="ADX1" t="inlineStr">
+      <c r="ADX1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_802</t>
         </is>
       </c>
-      <c r="ADY1" t="inlineStr">
+      <c r="ADY1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_803</t>
         </is>
       </c>
-      <c r="ADZ1" t="inlineStr">
+      <c r="ADZ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_804</t>
         </is>
       </c>
-      <c r="AEA1" t="inlineStr">
+      <c r="AEA1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_805</t>
         </is>
       </c>
-      <c r="AEB1" t="inlineStr">
+      <c r="AEB1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_806</t>
         </is>
       </c>
-      <c r="AEC1" t="inlineStr">
+      <c r="AEC1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_807</t>
         </is>
       </c>
-      <c r="AED1" t="inlineStr">
+      <c r="AED1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_808</t>
         </is>
       </c>
-      <c r="AEE1" t="inlineStr">
+      <c r="AEE1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_809</t>
         </is>
       </c>
-      <c r="AEF1" t="inlineStr">
+      <c r="AEF1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_810</t>
         </is>
       </c>
-      <c r="AEG1" t="inlineStr">
+      <c r="AEG1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_811</t>
         </is>
       </c>
-      <c r="AEH1" t="inlineStr">
+      <c r="AEH1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_812</t>
         </is>
       </c>
-      <c r="AEI1" t="inlineStr">
+      <c r="AEI1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_813</t>
         </is>
       </c>
-      <c r="AEJ1" t="inlineStr">
+      <c r="AEJ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_814</t>
         </is>
       </c>
-      <c r="AEK1" t="inlineStr">
+      <c r="AEK1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_815</t>
         </is>
       </c>
-      <c r="AEL1" t="inlineStr">
+      <c r="AEL1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_816</t>
         </is>
       </c>
-      <c r="AEM1" t="inlineStr">
+      <c r="AEM1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_817</t>
         </is>
       </c>
-      <c r="AEN1" t="inlineStr">
+      <c r="AEN1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_818</t>
         </is>
       </c>
-      <c r="AEO1" t="inlineStr">
+      <c r="AEO1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_819</t>
         </is>
       </c>
-      <c r="AEP1" t="inlineStr">
+      <c r="AEP1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_820</t>
         </is>
       </c>
-      <c r="AEQ1" t="inlineStr">
+      <c r="AEQ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_821</t>
         </is>
       </c>
-      <c r="AER1" t="inlineStr">
+      <c r="AER1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_822</t>
         </is>
       </c>
-      <c r="AES1" t="inlineStr">
+      <c r="AES1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_823</t>
         </is>
       </c>
-      <c r="AET1" t="inlineStr">
+      <c r="AET1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_824</t>
         </is>
       </c>
-      <c r="AEU1" t="inlineStr">
+      <c r="AEU1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_825</t>
         </is>
       </c>
-      <c r="AEV1" t="inlineStr">
+      <c r="AEV1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_826</t>
         </is>
       </c>
-      <c r="AEW1" t="inlineStr">
+      <c r="AEW1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_827</t>
         </is>
       </c>
-      <c r="AEX1" t="inlineStr">
+      <c r="AEX1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_828</t>
         </is>
       </c>
-      <c r="AEY1" t="inlineStr">
+      <c r="AEY1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_829</t>
         </is>
       </c>
-      <c r="AEZ1" t="inlineStr">
+      <c r="AEZ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_830</t>
         </is>
       </c>
-      <c r="AFA1" t="inlineStr">
+      <c r="AFA1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_831</t>
         </is>
       </c>
-      <c r="AFB1" t="inlineStr">
+      <c r="AFB1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_832</t>
         </is>
       </c>
-      <c r="AFC1" t="inlineStr">
+      <c r="AFC1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_833</t>
         </is>
       </c>
-      <c r="AFD1" t="inlineStr">
+      <c r="AFD1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_834</t>
         </is>
       </c>
-      <c r="AFE1" t="inlineStr">
+      <c r="AFE1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_835</t>
         </is>
       </c>
-      <c r="AFF1" t="inlineStr">
+      <c r="AFF1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_836</t>
         </is>
       </c>
-      <c r="AFG1" t="inlineStr">
+      <c r="AFG1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_837</t>
         </is>
       </c>
-      <c r="AFH1" t="inlineStr">
+      <c r="AFH1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_838</t>
         </is>
       </c>
-      <c r="AFI1" t="inlineStr">
+      <c r="AFI1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_839</t>
         </is>
       </c>
-      <c r="AFJ1" t="inlineStr">
+      <c r="AFJ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_840</t>
         </is>
       </c>
-      <c r="AFK1" t="inlineStr">
+      <c r="AFK1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_841</t>
         </is>
       </c>
-      <c r="AFL1" t="inlineStr">
+      <c r="AFL1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_842</t>
         </is>
       </c>
-      <c r="AFM1" t="inlineStr">
+      <c r="AFM1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_843</t>
         </is>
       </c>
-      <c r="AFN1" t="inlineStr">
+      <c r="AFN1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_844</t>
         </is>
       </c>
-      <c r="AFO1" t="inlineStr">
+      <c r="AFO1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_845</t>
         </is>
       </c>
-      <c r="AFP1" t="inlineStr">
+      <c r="AFP1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_846</t>
         </is>
       </c>
-      <c r="AFQ1" t="inlineStr">
+      <c r="AFQ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_847</t>
         </is>
       </c>
-      <c r="AFR1" t="inlineStr">
+      <c r="AFR1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_848</t>
         </is>
       </c>
-      <c r="AFS1" t="inlineStr">
+      <c r="AFS1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_849</t>
         </is>
       </c>
-      <c r="AFT1" t="inlineStr">
+      <c r="AFT1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_850</t>
         </is>
       </c>
-      <c r="AFU1" t="inlineStr">
+      <c r="AFU1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_851</t>
         </is>
       </c>
-      <c r="AFV1" t="inlineStr">
+      <c r="AFV1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_852</t>
         </is>
       </c>
-      <c r="AFW1" t="inlineStr">
+      <c r="AFW1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_853</t>
         </is>
       </c>
-      <c r="AFX1" t="inlineStr">
+      <c r="AFX1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_854</t>
         </is>
       </c>
-      <c r="AFY1" t="inlineStr">
+      <c r="AFY1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_855</t>
         </is>
       </c>
-      <c r="AFZ1" t="inlineStr">
+      <c r="AFZ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_856</t>
         </is>
       </c>
-      <c r="AGA1" t="inlineStr">
+      <c r="AGA1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_857</t>
         </is>
       </c>
-      <c r="AGB1" t="inlineStr">
+      <c r="AGB1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_858</t>
         </is>
       </c>
-      <c r="AGC1" t="inlineStr">
+      <c r="AGC1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_859</t>
         </is>
       </c>
-      <c r="AGD1" t="inlineStr">
+      <c r="AGD1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_860</t>
         </is>
       </c>
-      <c r="AGE1" t="inlineStr">
+      <c r="AGE1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_861</t>
         </is>
       </c>
-      <c r="AGF1" t="inlineStr">
+      <c r="AGF1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_862</t>
         </is>
       </c>
-      <c r="AGG1" t="inlineStr">
+      <c r="AGG1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_863</t>
         </is>
       </c>
-      <c r="AGH1" t="inlineStr">
+      <c r="AGH1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_864</t>
         </is>
       </c>
-      <c r="AGI1" t="inlineStr">
+      <c r="AGI1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_865</t>
         </is>
       </c>
-      <c r="AGJ1" t="inlineStr">
+      <c r="AGJ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_866</t>
         </is>
       </c>
-      <c r="AGK1" t="inlineStr">
+      <c r="AGK1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_867</t>
         </is>
       </c>
-      <c r="AGL1" t="inlineStr">
+      <c r="AGL1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_868</t>
         </is>
       </c>
-      <c r="AGM1" t="inlineStr">
+      <c r="AGM1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_869</t>
         </is>
       </c>
-      <c r="AGN1" t="inlineStr">
+      <c r="AGN1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_870</t>
         </is>
       </c>
-      <c r="AGO1" t="inlineStr">
+      <c r="AGO1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_871</t>
         </is>
       </c>
-      <c r="AGP1" t="inlineStr">
+      <c r="AGP1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_872</t>
         </is>
       </c>
-      <c r="AGQ1" t="inlineStr">
+      <c r="AGQ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_873</t>
         </is>
       </c>
-      <c r="AGR1" t="inlineStr">
+      <c r="AGR1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_874</t>
         </is>
       </c>
-      <c r="AGS1" t="inlineStr">
+      <c r="AGS1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_875</t>
         </is>
       </c>
-      <c r="AGT1" t="inlineStr">
+      <c r="AGT1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_876</t>
         </is>
       </c>
-      <c r="AGU1" t="inlineStr">
+      <c r="AGU1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_877</t>
         </is>
       </c>
-      <c r="AGV1" t="inlineStr">
+      <c r="AGV1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_878</t>
         </is>
       </c>
-      <c r="AGW1" t="inlineStr">
+      <c r="AGW1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_879</t>
         </is>
       </c>
-      <c r="AGX1" t="inlineStr">
+      <c r="AGX1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_880</t>
         </is>
       </c>
-      <c r="AGY1" t="inlineStr">
+      <c r="AGY1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_881</t>
         </is>
       </c>
-      <c r="AGZ1" t="inlineStr">
+      <c r="AGZ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_882</t>
         </is>
       </c>
-      <c r="AHA1" t="inlineStr">
+      <c r="AHA1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_883</t>
         </is>
       </c>
-      <c r="AHB1" t="inlineStr">
+      <c r="AHB1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_884</t>
         </is>
       </c>
-      <c r="AHC1" t="inlineStr">
+      <c r="AHC1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_885</t>
         </is>
       </c>
-      <c r="AHD1" t="inlineStr">
+      <c r="AHD1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_886</t>
         </is>
       </c>
-      <c r="AHE1" t="inlineStr">
+      <c r="AHE1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_887</t>
         </is>
       </c>
-      <c r="AHF1" t="inlineStr">
+      <c r="AHF1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_888</t>
         </is>
       </c>
-      <c r="AHG1" t="inlineStr">
+      <c r="AHG1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_889</t>
         </is>
       </c>
-      <c r="AHH1" t="inlineStr">
+      <c r="AHH1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_890</t>
         </is>
       </c>
-      <c r="AHI1" t="inlineStr">
+      <c r="AHI1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_891</t>
         </is>
       </c>
-      <c r="AHJ1" t="inlineStr">
+      <c r="AHJ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_892</t>
         </is>
       </c>
-      <c r="AHK1" t="inlineStr">
+      <c r="AHK1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_893</t>
         </is>
       </c>
-      <c r="AHL1" t="inlineStr">
+      <c r="AHL1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_894</t>
         </is>
       </c>
-      <c r="AHM1" t="inlineStr">
+      <c r="AHM1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_895</t>
         </is>
       </c>
-      <c r="AHN1" t="inlineStr">
+      <c r="AHN1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_896</t>
         </is>
       </c>
-      <c r="AHO1" t="inlineStr">
+      <c r="AHO1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_897</t>
         </is>
       </c>
-      <c r="AHP1" t="inlineStr">
+      <c r="AHP1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_898</t>
         </is>
       </c>
-      <c r="AHQ1" t="inlineStr">
+      <c r="AHQ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_899</t>
         </is>
       </c>
-      <c r="AHR1" t="inlineStr">
+      <c r="AHR1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_900</t>
         </is>
       </c>
-      <c r="AHS1" t="inlineStr">
+      <c r="AHS1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_901</t>
         </is>
       </c>
-      <c r="AHT1" t="inlineStr">
+      <c r="AHT1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_902</t>
         </is>
       </c>
-      <c r="AHU1" t="inlineStr">
+      <c r="AHU1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_903</t>
         </is>
       </c>
-      <c r="AHV1" t="inlineStr">
+      <c r="AHV1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_904</t>
         </is>
       </c>
-      <c r="AHW1" t="inlineStr">
+      <c r="AHW1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_905</t>
         </is>
       </c>
-      <c r="AHX1" t="inlineStr">
+      <c r="AHX1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_906</t>
         </is>
       </c>
-      <c r="AHY1" t="inlineStr">
+      <c r="AHY1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_907</t>
         </is>
       </c>
-      <c r="AHZ1" t="inlineStr">
+      <c r="AHZ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_908</t>
         </is>
       </c>
-      <c r="AIA1" t="inlineStr">
+      <c r="AIA1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_909</t>
         </is>
       </c>
-      <c r="AIB1" t="inlineStr">
+      <c r="AIB1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_910</t>
         </is>
       </c>
-      <c r="AIC1" t="inlineStr">
+      <c r="AIC1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_911</t>
         </is>
       </c>
-      <c r="AID1" t="inlineStr">
+      <c r="AID1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_912</t>
         </is>
       </c>
-      <c r="AIE1" t="inlineStr">
+      <c r="AIE1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_913</t>
         </is>
       </c>
-      <c r="AIF1" t="inlineStr">
+      <c r="AIF1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_914</t>
         </is>
       </c>
-      <c r="AIG1" t="inlineStr">
+      <c r="AIG1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_915</t>
         </is>
       </c>
-      <c r="AIH1" t="inlineStr">
+      <c r="AIH1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_916</t>
         </is>
       </c>
-      <c r="AII1" t="inlineStr">
+      <c r="AII1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_917</t>
         </is>
       </c>
-      <c r="AIJ1" t="inlineStr">
+      <c r="AIJ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_918</t>
         </is>
       </c>
-      <c r="AIK1" t="inlineStr">
+      <c r="AIK1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_919</t>
         </is>
       </c>
-      <c r="AIL1" t="inlineStr">
+      <c r="AIL1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_920</t>
         </is>
       </c>
-      <c r="AIM1" t="inlineStr">
+      <c r="AIM1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_921</t>
         </is>
       </c>
-      <c r="AIN1" t="inlineStr">
+      <c r="AIN1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_922</t>
         </is>
       </c>
-      <c r="AIO1" t="inlineStr">
+      <c r="AIO1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_923</t>
         </is>
       </c>
-      <c r="AIP1" t="inlineStr">
+      <c r="AIP1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_924</t>
         </is>
       </c>
-      <c r="AIQ1" t="inlineStr">
+      <c r="AIQ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_925</t>
         </is>
       </c>
-      <c r="AIR1" t="inlineStr">
+      <c r="AIR1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_926</t>
         </is>
       </c>
-      <c r="AIS1" t="inlineStr">
+      <c r="AIS1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_927</t>
         </is>
       </c>
-      <c r="AIT1" t="inlineStr">
+      <c r="AIT1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_928</t>
         </is>
       </c>
-      <c r="AIU1" t="inlineStr">
+      <c r="AIU1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_929</t>
         </is>
       </c>
-      <c r="AIV1" t="inlineStr">
+      <c r="AIV1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_930</t>
         </is>
       </c>
-      <c r="AIW1" t="inlineStr">
+      <c r="AIW1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_931</t>
         </is>
       </c>
-      <c r="AIX1" t="inlineStr">
+      <c r="AIX1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_932</t>
         </is>
       </c>
-      <c r="AIY1" t="inlineStr">
+      <c r="AIY1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_933</t>
         </is>
       </c>
-      <c r="AIZ1" t="inlineStr">
+      <c r="AIZ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_934</t>
         </is>
       </c>
-      <c r="AJA1" t="inlineStr">
+      <c r="AJA1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_935</t>
         </is>
       </c>
-      <c r="AJB1" t="inlineStr">
+      <c r="AJB1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_936</t>
         </is>
       </c>
-      <c r="AJC1" t="inlineStr">
+      <c r="AJC1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_937</t>
         </is>
       </c>
-      <c r="AJD1" t="inlineStr">
+      <c r="AJD1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_938</t>
         </is>
       </c>
-      <c r="AJE1" t="inlineStr">
+      <c r="AJE1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_939</t>
         </is>
       </c>
-      <c r="AJF1" t="inlineStr">
+      <c r="AJF1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_940</t>
         </is>
       </c>
-      <c r="AJG1" t="inlineStr">
+      <c r="AJG1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_941</t>
         </is>
       </c>
-      <c r="AJH1" t="inlineStr">
+      <c r="AJH1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_942</t>
         </is>
       </c>
-      <c r="AJI1" t="inlineStr">
+      <c r="AJI1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_943</t>
         </is>
       </c>
-      <c r="AJJ1" t="inlineStr">
+      <c r="AJJ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_944</t>
         </is>
       </c>
-      <c r="AJK1" t="inlineStr">
+      <c r="AJK1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_945</t>
         </is>
       </c>
-      <c r="AJL1" t="inlineStr">
+      <c r="AJL1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_946</t>
         </is>
       </c>
-      <c r="AJM1" t="inlineStr">
+      <c r="AJM1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_947</t>
         </is>
       </c>
-      <c r="AJN1" t="inlineStr">
+      <c r="AJN1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_948</t>
         </is>
       </c>
-      <c r="AJO1" t="inlineStr">
+      <c r="AJO1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_949</t>
         </is>
       </c>
-      <c r="AJP1" t="inlineStr">
+      <c r="AJP1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_950</t>
         </is>
       </c>
-      <c r="AJQ1" t="inlineStr">
+      <c r="AJQ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_951</t>
         </is>
       </c>
-      <c r="AJR1" t="inlineStr">
+      <c r="AJR1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_952</t>
         </is>
       </c>
-      <c r="AJS1" t="inlineStr">
+      <c r="AJS1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_953</t>
         </is>
       </c>
-      <c r="AJT1" t="inlineStr">
+      <c r="AJT1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_954</t>
         </is>
       </c>
-      <c r="AJU1" t="inlineStr">
+      <c r="AJU1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_955</t>
         </is>
       </c>
-      <c r="AJV1" t="inlineStr">
+      <c r="AJV1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_956</t>
         </is>
       </c>
-      <c r="AJW1" t="inlineStr">
+      <c r="AJW1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_957</t>
         </is>
       </c>
-      <c r="AJX1" t="inlineStr">
+      <c r="AJX1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_958</t>
         </is>
       </c>
-      <c r="AJY1" t="inlineStr">
+      <c r="AJY1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_959</t>
         </is>
       </c>
-      <c r="AJZ1" t="inlineStr">
+      <c r="AJZ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_960</t>
         </is>
       </c>
-      <c r="AKA1" t="inlineStr">
+      <c r="AKA1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_961</t>
         </is>
       </c>
-      <c r="AKB1" t="inlineStr">
+      <c r="AKB1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_962</t>
         </is>
       </c>
-      <c r="AKC1" t="inlineStr">
+      <c r="AKC1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_963</t>
         </is>
       </c>
-      <c r="AKD1" t="inlineStr">
+      <c r="AKD1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_964</t>
         </is>
       </c>
-      <c r="AKE1" t="inlineStr">
+      <c r="AKE1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_965</t>
         </is>
       </c>
-      <c r="AKF1" t="inlineStr">
+      <c r="AKF1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_966</t>
         </is>
       </c>
-      <c r="AKG1" t="inlineStr">
+      <c r="AKG1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_967</t>
         </is>
       </c>
-      <c r="AKH1" t="inlineStr">
+      <c r="AKH1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_968</t>
         </is>
       </c>
-      <c r="AKI1" t="inlineStr">
+      <c r="AKI1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_969</t>
         </is>
       </c>
-      <c r="AKJ1" t="inlineStr">
+      <c r="AKJ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_970</t>
         </is>
       </c>
-      <c r="AKK1" t="inlineStr">
+      <c r="AKK1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_971</t>
         </is>
       </c>
-      <c r="AKL1" t="inlineStr">
+      <c r="AKL1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_972</t>
         </is>
       </c>
-      <c r="AKM1" t="inlineStr">
+      <c r="AKM1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_973</t>
         </is>
       </c>
-      <c r="AKN1" t="inlineStr">
+      <c r="AKN1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_974</t>
         </is>
       </c>
-      <c r="AKO1" t="inlineStr">
+      <c r="AKO1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_975</t>
         </is>
       </c>
-      <c r="AKP1" t="inlineStr">
+      <c r="AKP1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_976</t>
         </is>
       </c>
-      <c r="AKQ1" t="inlineStr">
+      <c r="AKQ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_977</t>
         </is>
       </c>
-      <c r="AKR1" t="inlineStr">
+      <c r="AKR1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_978</t>
         </is>
       </c>
-      <c r="AKS1" t="inlineStr">
+      <c r="AKS1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_979</t>
         </is>
       </c>
-      <c r="AKT1" t="inlineStr">
+      <c r="AKT1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_980</t>
         </is>
       </c>
-      <c r="AKU1" t="inlineStr">
+      <c r="AKU1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_981</t>
         </is>
       </c>
-      <c r="AKV1" t="inlineStr">
+      <c r="AKV1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_982</t>
         </is>
       </c>
-      <c r="AKW1" t="inlineStr">
+      <c r="AKW1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_983</t>
         </is>
       </c>
-      <c r="AKX1" t="inlineStr">
+      <c r="AKX1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_984</t>
         </is>
       </c>
-      <c r="AKY1" t="inlineStr">
+      <c r="AKY1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_985</t>
         </is>
       </c>
-      <c r="AKZ1" t="inlineStr">
+      <c r="AKZ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_986</t>
         </is>
       </c>
-      <c r="ALA1" t="inlineStr">
+      <c r="ALA1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_987</t>
         </is>
       </c>
-      <c r="ALB1" t="inlineStr">
+      <c r="ALB1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_988</t>
         </is>
       </c>
-      <c r="ALC1" t="inlineStr">
+      <c r="ALC1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_989</t>
         </is>
       </c>
-      <c r="ALD1" t="inlineStr">
+      <c r="ALD1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_990</t>
         </is>
       </c>
-      <c r="ALE1" t="inlineStr">
+      <c r="ALE1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_991</t>
         </is>
       </c>
-      <c r="ALF1" t="inlineStr">
+      <c r="ALF1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_992</t>
         </is>
       </c>
-      <c r="ALG1" t="inlineStr">
+      <c r="ALG1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_993</t>
         </is>
       </c>
-      <c r="ALH1" t="inlineStr">
+      <c r="ALH1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_994</t>
         </is>
       </c>
-      <c r="ALI1" t="inlineStr">
+      <c r="ALI1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_995</t>
         </is>
       </c>
-      <c r="ALJ1" t="inlineStr">
+      <c r="ALJ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_996</t>
         </is>
       </c>
-      <c r="ALK1" t="inlineStr">
+      <c r="ALK1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_997</t>
         </is>
       </c>
-      <c r="ALL1" t="inlineStr">
+      <c r="ALL1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_998</t>
         </is>
       </c>
-      <c r="ALM1" t="inlineStr">
+      <c r="ALM1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_999</t>
         </is>
       </c>
-      <c r="ALN1" t="inlineStr">
+      <c r="ALN1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_1000</t>
         </is>
       </c>
-      <c r="ALO1" t="inlineStr">
+      <c r="ALO1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_1001</t>
         </is>
       </c>
-      <c r="ALP1" t="inlineStr">
+      <c r="ALP1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_1002</t>
         </is>
       </c>
-      <c r="ALQ1" t="inlineStr">
+      <c r="ALQ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_1003</t>
         </is>
       </c>
-      <c r="ALR1" t="inlineStr">
+      <c r="ALR1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_1004</t>
         </is>
       </c>
-      <c r="ALS1" t="inlineStr">
+      <c r="ALS1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_1005</t>
         </is>
       </c>
-      <c r="ALT1" t="inlineStr">
+      <c r="ALT1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_1006</t>
         </is>
       </c>
-      <c r="ALU1" t="inlineStr">
+      <c r="ALU1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_1007</t>
         </is>
       </c>
-      <c r="ALV1" t="inlineStr">
+      <c r="ALV1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_1008</t>
         </is>
       </c>
-      <c r="ALW1" t="inlineStr">
+      <c r="ALW1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_1009</t>
         </is>
       </c>
-      <c r="ALX1" t="inlineStr">
+      <c r="ALX1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_1010</t>
         </is>
       </c>
-      <c r="ALY1" t="inlineStr">
+      <c r="ALY1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_1011</t>
         </is>
       </c>
-      <c r="ALZ1" t="inlineStr">
+      <c r="ALZ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_1012</t>
         </is>
       </c>
-      <c r="AMA1" t="inlineStr">
+      <c r="AMA1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_1013</t>
         </is>
       </c>
-      <c r="AMB1" t="inlineStr">
+      <c r="AMB1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_1014</t>
         </is>
       </c>
-      <c r="AMC1" t="inlineStr">
+      <c r="AMC1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_1015</t>
         </is>
       </c>
-      <c r="AMD1" t="inlineStr">
+      <c r="AMD1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_1016</t>
         </is>
       </c>
-      <c r="AME1" t="inlineStr">
+      <c r="AME1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_1017</t>
         </is>
       </c>
-      <c r="AMF1" t="inlineStr">
+      <c r="AMF1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_1018</t>
         </is>
       </c>
-      <c r="AMG1" t="inlineStr">
+      <c r="AMG1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_1019</t>
         </is>
       </c>
-      <c r="AMH1" t="inlineStr">
+      <c r="AMH1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_1020</t>
         </is>
       </c>
-      <c r="AMI1" t="inlineStr">
+      <c r="AMI1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_1021</t>
         </is>
       </c>
-      <c r="AMJ1" t="inlineStr">
+      <c r="AMJ1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_1022</t>
         </is>
       </c>
-      <c r="AMK1" t="inlineStr">
+      <c r="AMK1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_1023</t>
         </is>
       </c>
-      <c r="AML1" t="inlineStr">
+      <c r="AML1" s="1" t="inlineStr">
         <is>
           <t>ECFP6_1024</t>
         </is>
